--- a/docs/tai-ve/Phan-tich-khoi-luong-MD-APIC.xlsx
+++ b/docs/tai-ve/Phan-tich-khoi-luong-MD-APIC.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1999" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2002" uniqueCount="443">
   <si>
     <t xml:space="preserve">Phân công dự kiến nhóm MD APIC (quyết định 10/2026)</t>
   </si>
@@ -325,7 +325,7 @@
     <t xml:space="preserve">Theo dõi thêm</t>
   </si>
   <si>
-    <t xml:space="preserve">Chỉ số tải nhóm MD – kỳ hiện tại (bulk 26FW + 27SS, mẫu 27SS)</t>
+    <t xml:space="preserve">Chỉ số tải nhóm MD – kỳ vừa qua (bulk 26FW + 27SS, mẫu 27SS)</t>
   </si>
   <si>
     <t xml:space="preserve">Ô vàng chữ xanh = số đầu vào (đã nhân hệ số độ khó ALLTERRAIN/DESCENTE × 1,3) và trọng số; có thể sửa. Các cột chỉ số là công thức. 1,0 = trung bình 6 MD làm đủ kỳ.</t>
@@ -433,7 +433,7 @@
     <t xml:space="preserve">Phương án</t>
   </si>
   <si>
-    <t xml:space="preserve">GĐ1 (đến hết mẫu triển lãm 27FW). 0. Chưa chia việc Luan</t>
+    <t xml:space="preserve">GĐ1 (hiện tại: bulk 27SS, mẫu triển lãm 27FW, PPS 27SS). 0. Chưa chia việc Luan</t>
   </si>
   <si>
     <r>
@@ -467,7 +467,66 @@
     <t xml:space="preserve">GĐ1. Khanh làm hậu cần + hỗ trợ dịch (~25% việc Luan)</t>
   </si>
   <si>
-    <t xml:space="preserve">GĐ2 (1st 28SS). Khanh 1/3 mẫu TNF + hậu cần (~15%)</t>
+    <t xml:space="preserve">GĐ1. Khanh hỗ trợ ~35% việc Luan</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GĐ1. Khanh hỗ trợ ~25% việc Luan + nhận TNF </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">東京企画 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ngay</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GĐ1. Khanh hỗ trợ ~35% việc Luan + nhận TNF </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">東京企画 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ngay</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">GĐ2 (mẫu phát triển, 1st 28SS). Khanh 1/3 mẫu TNF + hậu cần (~15%)</t>
   </si>
   <si>
     <t xml:space="preserve">GĐ2. + Khanh hỗ trợ dịch (~25% việc Luan)</t>
@@ -538,7 +597,7 @@
     <t xml:space="preserve">Tô đỏ: chỉ số ≥ 1,4 (vượt mức tăng ca 1 giờ/ngày, cần chia việc).</t>
   </si>
   <si>
-    <t xml:space="preserve">GĐ1: mẫu triển lãm 27FW ước bằng SMS 26FW × 40% (chỉ còn theo dõi tiến độ, dịch góp ý). GĐ2: mẫu 1st 28SS ước bằng 1st–3rd 27SS.</t>
+    <t xml:space="preserve">Bulk 26FW không tính (đã xong trên 95%). GĐ1: mẫu triển lãm 27FW ước bằng SMS 26FW × 40% (chỉ còn theo dõi tiến độ, dịch góp ý) + mẫu PPS 27SS (1 cái/mã bulk + 5% tái PPS). GĐ2: mẫu phát triển, 1st 28SS ước bằng 1st–3rd 27SS.</t>
   </si>
   <si>
     <t xml:space="preserve">Bich Trang ở GĐ2 bị tính thấp: file BULK chưa có bulk 27SS của FOXFIRE, TATRAS, Kasco, YONEX.</t>
@@ -4185,7 +4244,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="62"/>
@@ -4228,30 +4287,30 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B5" s="13" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="D5" s="10" t="n">
         <v>0.15</v>
       </c>
-      <c r="E5" s="13" t="n">
-        <v>1.43</v>
+      <c r="E5" s="10" t="n">
+        <v>1.17</v>
       </c>
       <c r="F5" s="10" t="n">
         <v>1.14</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.85</v>
+        <v>0.96</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4259,25 +4318,25 @@
         <v>68</v>
       </c>
       <c r="B6" s="13" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E6" s="13" t="n">
-        <v>1.43</v>
+        <v>0.41</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>1.17</v>
       </c>
       <c r="F6" s="10" t="n">
         <v>1.14</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>0.85</v>
+        <v>0.96</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4285,25 +4344,25 @@
         <v>69</v>
       </c>
       <c r="B7" s="13" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E7" s="13" t="n">
-        <v>1.43</v>
+        <v>0.59</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>1.17</v>
       </c>
       <c r="F7" s="10" t="n">
         <v>1.14</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.85</v>
+        <v>0.96</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4311,51 +4370,51 @@
         <v>70</v>
       </c>
       <c r="B8" s="13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="C8" s="13" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>1.13</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.53</v>
+        <v>0.76</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0.32</v>
+        <v>1.17</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1.39</v>
+        <v>1.14</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>1.13</v>
+        <v>0.96</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>0.87</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="C9" s="13" t="n">
-        <v>1.41</v>
+      <c r="B9" s="10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>1.3</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.32</v>
+        <v>1.17</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1.39</v>
+        <v>1.14</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>1.13</v>
+        <v>0.96</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.87</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4363,25 +4422,25 @@
         <v>72</v>
       </c>
       <c r="B10" s="10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="C10" s="13" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>1.13</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.7</v>
+        <v>0.97</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>0.32</v>
+        <v>1.17</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1.39</v>
+        <v>1.14</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>1.13</v>
+        <v>0.96</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>0.87</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4391,11 +4450,11 @@
       <c r="B11" s="13" t="n">
         <v>1.41</v>
       </c>
-      <c r="C11" s="10" t="n">
-        <v>1.22</v>
+      <c r="C11" s="13" t="n">
+        <v>1.6</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>0.91</v>
+        <v>0.53</v>
       </c>
       <c r="E11" s="10" t="n">
         <v>0.32</v>
@@ -4411,49 +4470,127 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="10" t="n">
         <v>1.24</v>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C13" s="13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C14" s="10" t="n">
         <v>1.22</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D14" s="10" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="D15" s="11" t="n">
         <v>1.08</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E15" s="11" t="n">
         <v>0.32</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F15" s="11" t="n">
         <v>1.39</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G15" s="11" t="n">
         <v>1.13</v>
       </c>
-      <c r="H12" s="11" t="n">
+      <c r="H15" s="11" t="n">
         <v>0.87</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="12" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -4481,12 +4618,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4494,40 +4631,40 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4819,7 +4956,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B12" s="14" t="n">
         <f aca="false">SUM(B5:B11)</f>
@@ -4900,22 +5037,22 @@
         <v>2</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>5</v>
@@ -4923,13 +5060,13 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D2" s="16" t="n">
         <v>1581</v>
@@ -4947,13 +5084,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D3" s="16" t="n">
         <v>345</v>
@@ -4971,13 +5108,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D4" s="16" t="n">
         <v>400</v>
@@ -4995,13 +5132,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B5" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>104</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>101</v>
       </c>
       <c r="D5" s="16" t="n">
         <v>3679</v>
@@ -5019,13 +5156,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D6" s="16" t="n">
         <v>250</v>
@@ -5043,13 +5180,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D7" s="16" t="n">
         <v>2888</v>
@@ -5067,13 +5204,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D8" s="16" t="n">
         <v>3831</v>
@@ -5091,13 +5228,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D9" s="16" t="n">
         <v>355</v>
@@ -5115,13 +5252,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D10" s="16" t="n">
         <v>2596</v>
@@ -5139,13 +5276,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D11" s="16" t="n">
         <v>34077</v>
@@ -5163,13 +5300,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D12" s="16" t="n">
         <v>1469</v>
@@ -5187,13 +5324,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D13" s="16" t="n">
         <v>2888</v>
@@ -5211,13 +5348,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D14" s="16" t="n">
         <v>666</v>
@@ -5235,13 +5372,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D15" s="16" t="n">
         <v>278</v>
@@ -5259,13 +5396,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D16" s="16" t="n">
         <v>20226</v>
@@ -5283,13 +5420,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D17" s="16" t="n">
         <v>914</v>
@@ -5307,13 +5444,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D18" s="16" t="n">
         <v>548</v>
@@ -5331,13 +5468,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D19" s="16" t="n">
         <v>3782</v>
@@ -5355,13 +5492,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D20" s="16" t="n">
         <v>5400</v>
@@ -5379,13 +5516,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D21" s="16" t="n">
         <v>16154</v>
@@ -5403,13 +5540,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D22" s="16" t="n">
         <v>1050</v>
@@ -5427,13 +5564,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D23" s="16" t="n">
         <v>18185</v>
@@ -5451,13 +5588,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D24" s="16" t="n">
         <v>250</v>
@@ -5475,13 +5612,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D25" s="16" t="n">
         <v>12276</v>
@@ -5499,13 +5636,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D26" s="16" t="n">
         <v>821</v>
@@ -5523,13 +5660,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D27" s="16" t="n">
         <v>7355</v>
@@ -5550,10 +5687,10 @@
         <v>6</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D28" s="16" t="n">
         <v>9350</v>
@@ -5574,10 +5711,10 @@
         <v>6</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D29" s="16" t="n">
         <v>8892</v>
@@ -5598,10 +5735,10 @@
         <v>6</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D30" s="16" t="n">
         <v>1608</v>
@@ -5622,10 +5759,10 @@
         <v>6</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D31" s="16" t="n">
         <v>2000</v>
@@ -5646,10 +5783,10 @@
         <v>6</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D32" s="16" t="n">
         <v>50717</v>
@@ -5670,10 +5807,10 @@
         <v>6</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D33" s="16" t="n">
         <v>21965</v>
@@ -5694,10 +5831,10 @@
         <v>6</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D34" s="16" t="n">
         <v>11214</v>
@@ -5718,10 +5855,10 @@
         <v>6</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D35" s="16" t="n">
         <v>5815</v>
@@ -5742,10 +5879,10 @@
         <v>6</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D36" s="16" t="n">
         <v>2000</v>
@@ -5766,10 +5903,10 @@
         <v>6</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D37" s="16" t="n">
         <v>10763</v>
@@ -5790,10 +5927,10 @@
         <v>6</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D38" s="16" t="n">
         <v>9108</v>
@@ -5814,10 +5951,10 @@
         <v>6</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D39" s="16" t="n">
         <v>9120</v>
@@ -5838,10 +5975,10 @@
         <v>6</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D40" s="16" t="n">
         <v>13557</v>
@@ -5862,10 +5999,10 @@
         <v>6</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D41" s="16" t="n">
         <v>30496</v>
@@ -5886,10 +6023,10 @@
         <v>6</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D42" s="16" t="n">
         <v>7227</v>
@@ -5910,10 +6047,10 @@
         <v>6</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D43" s="16" t="n">
         <v>1701</v>
@@ -5934,10 +6071,10 @@
         <v>6</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D44" s="16" t="n">
         <v>16804</v>
@@ -5958,10 +6095,10 @@
         <v>6</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D45" s="16" t="n">
         <v>12067</v>
@@ -5982,10 +6119,10 @@
         <v>6</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D46" s="16" t="n">
         <v>329</v>
@@ -6006,10 +6143,10 @@
         <v>6</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D47" s="16" t="n">
         <v>20674</v>
@@ -6030,10 +6167,10 @@
         <v>6</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D48" s="16" t="n">
         <v>6003</v>
@@ -6054,10 +6191,10 @@
         <v>6</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D49" s="16" t="n">
         <v>150</v>
@@ -6078,10 +6215,10 @@
         <v>6</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D50" s="16" t="n">
         <v>21124</v>
@@ -6102,10 +6239,10 @@
         <v>6</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D51" s="16" t="n">
         <v>5199</v>
@@ -6126,10 +6263,10 @@
         <v>6</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D52" s="16" t="n">
         <v>14544</v>
@@ -6150,10 +6287,10 @@
         <v>6</v>
       </c>
       <c r="B53" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="C53" s="15" t="s">
         <v>125</v>
-      </c>
-      <c r="C53" s="15" t="s">
-        <v>122</v>
       </c>
       <c r="D53" s="16" t="n">
         <v>15800</v>
@@ -6174,10 +6311,10 @@
         <v>6</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D54" s="16" t="n">
         <v>7795</v>
@@ -6198,10 +6335,10 @@
         <v>6</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D55" s="16" t="n">
         <v>29328</v>
@@ -6222,10 +6359,10 @@
         <v>6</v>
       </c>
       <c r="B56" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="C56" s="15" t="s">
         <v>126</v>
-      </c>
-      <c r="C56" s="15" t="s">
-        <v>123</v>
       </c>
       <c r="D56" s="16" t="n">
         <v>4882</v>
@@ -6246,10 +6383,10 @@
         <v>6</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D57" s="16" t="n">
         <v>6131</v>
@@ -6270,10 +6407,10 @@
         <v>6</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D58" s="16" t="n">
         <v>805</v>
@@ -6294,10 +6431,10 @@
         <v>6</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D59" s="16" t="n">
         <v>109487</v>
@@ -6318,10 +6455,10 @@
         <v>6</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D60" s="16" t="n">
         <v>26543</v>
@@ -6342,10 +6479,10 @@
         <v>6</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D61" s="16" t="n">
         <v>874</v>
@@ -6366,10 +6503,10 @@
         <v>6</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D62" s="16" t="n">
         <v>19320</v>
@@ -6390,10 +6527,10 @@
         <v>6</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D63" s="16" t="n">
         <v>4885</v>
@@ -6414,10 +6551,10 @@
         <v>6</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D64" s="16" t="n">
         <v>24694</v>
@@ -6438,10 +6575,10 @@
         <v>6</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D65" s="16" t="n">
         <v>35392</v>
@@ -6462,10 +6599,10 @@
         <v>6</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D66" s="16" t="n">
         <v>6450</v>
@@ -6486,10 +6623,10 @@
         <v>6</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D67" s="16" t="n">
         <v>18161</v>
@@ -6510,10 +6647,10 @@
         <v>6</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D68" s="16" t="n">
         <v>14612</v>
@@ -6534,10 +6671,10 @@
         <v>6</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D69" s="16" t="n">
         <v>5654</v>
@@ -6558,10 +6695,10 @@
         <v>6</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D70" s="16" t="n">
         <v>43447</v>
@@ -6582,10 +6719,10 @@
         <v>6</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D71" s="16" t="n">
         <v>518</v>
@@ -6606,10 +6743,10 @@
         <v>6</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D72" s="16" t="n">
         <v>41883</v>
@@ -6630,10 +6767,10 @@
         <v>6</v>
       </c>
       <c r="B73" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C73" s="15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D73" s="16" t="n">
         <v>4472</v>
@@ -6654,10 +6791,10 @@
         <v>6</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D74" s="16" t="n">
         <v>16462</v>
@@ -6678,10 +6815,10 @@
         <v>6</v>
       </c>
       <c r="B75" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D75" s="16" t="n">
         <v>2853</v>
@@ -6702,10 +6839,10 @@
         <v>6</v>
       </c>
       <c r="B76" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C76" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D76" s="16" t="n">
         <v>36373</v>
@@ -6720,7 +6857,7 @@
         <v>529</v>
       </c>
       <c r="H76" s="17" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6728,10 +6865,10 @@
         <v>6</v>
       </c>
       <c r="B77" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D77" s="16" t="n">
         <v>3465</v>
@@ -6752,10 +6889,10 @@
         <v>6</v>
       </c>
       <c r="B78" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C78" s="15" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D78" s="16" t="n">
         <v>18885</v>
@@ -6776,10 +6913,10 @@
         <v>6</v>
       </c>
       <c r="B79" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D79" s="16" t="n">
         <v>940</v>
@@ -6800,10 +6937,10 @@
         <v>6</v>
       </c>
       <c r="B80" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D80" s="16" t="n">
         <v>28995</v>
@@ -6824,10 +6961,10 @@
         <v>25</v>
       </c>
       <c r="B81" s="15" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D81" s="16" t="n">
         <v>1476</v>
@@ -6848,10 +6985,10 @@
         <v>25</v>
       </c>
       <c r="B82" s="15" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D82" s="16" t="n">
         <v>15886</v>
@@ -6872,10 +7009,10 @@
         <v>25</v>
       </c>
       <c r="B83" s="15" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D83" s="16" t="n">
         <v>3911</v>
@@ -6896,10 +7033,10 @@
         <v>25</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D84" s="16" t="n">
         <v>2632</v>
@@ -6920,10 +7057,10 @@
         <v>25</v>
       </c>
       <c r="B85" s="15" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D85" s="16" t="n">
         <v>9594</v>
@@ -6944,10 +7081,10 @@
         <v>25</v>
       </c>
       <c r="B86" s="15" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D86" s="16" t="n">
         <v>1382</v>
@@ -6968,10 +7105,10 @@
         <v>25</v>
       </c>
       <c r="B87" s="15" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D87" s="16" t="n">
         <v>4988</v>
@@ -6992,10 +7129,10 @@
         <v>25</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D88" s="16" t="n">
         <v>5931</v>
@@ -7016,10 +7153,10 @@
         <v>25</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D89" s="16" t="n">
         <v>1630</v>
@@ -7040,10 +7177,10 @@
         <v>25</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D90" s="16" t="n">
         <v>3380</v>
@@ -7064,10 +7201,10 @@
         <v>25</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D91" s="16" t="n">
         <v>1610</v>
@@ -7088,10 +7225,10 @@
         <v>25</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D92" s="16" t="n">
         <v>5931</v>
@@ -7112,10 +7249,10 @@
         <v>25</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D93" s="16" t="n">
         <v>772</v>
@@ -7136,10 +7273,10 @@
         <v>25</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D94" s="16" t="n">
         <v>16784</v>
@@ -7160,10 +7297,10 @@
         <v>25</v>
       </c>
       <c r="B95" s="15" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C95" s="15" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D95" s="16" t="n">
         <v>1484</v>
@@ -7184,10 +7321,10 @@
         <v>25</v>
       </c>
       <c r="B96" s="15" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D96" s="16" t="n">
         <v>301</v>
@@ -7208,10 +7345,10 @@
         <v>25</v>
       </c>
       <c r="B97" s="15" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D97" s="16" t="n">
         <v>7592</v>
@@ -7232,10 +7369,10 @@
         <v>25</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D98" s="16" t="n">
         <v>998</v>
@@ -7256,10 +7393,10 @@
         <v>25</v>
       </c>
       <c r="B99" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D99" s="16" t="n">
         <v>4455</v>
@@ -7280,10 +7417,10 @@
         <v>25</v>
       </c>
       <c r="B100" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D100" s="16" t="n">
         <v>13869</v>
@@ -7304,10 +7441,10 @@
         <v>25</v>
       </c>
       <c r="B101" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C101" s="15" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D101" s="16" t="n">
         <v>10000</v>
@@ -7328,10 +7465,10 @@
         <v>25</v>
       </c>
       <c r="B102" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D102" s="16" t="n">
         <v>20608</v>
@@ -7352,10 +7489,10 @@
         <v>25</v>
       </c>
       <c r="B103" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C103" s="15" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D103" s="16" t="n">
         <v>7683</v>
@@ -7376,10 +7513,10 @@
         <v>25</v>
       </c>
       <c r="B104" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C104" s="15" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D104" s="16" t="n">
         <v>5065</v>
@@ -7400,10 +7537,10 @@
         <v>25</v>
       </c>
       <c r="B105" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C105" s="15" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D105" s="16" t="n">
         <v>10117</v>
@@ -7424,10 +7561,10 @@
         <v>25</v>
       </c>
       <c r="B106" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D106" s="16" t="n">
         <v>966</v>
@@ -7448,10 +7585,10 @@
         <v>25</v>
       </c>
       <c r="B107" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C107" s="15" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D107" s="16" t="n">
         <v>25802</v>
@@ -7472,10 +7609,10 @@
         <v>25</v>
       </c>
       <c r="B108" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C108" s="15" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D108" s="16" t="n">
         <v>655</v>
@@ -7496,10 +7633,10 @@
         <v>25</v>
       </c>
       <c r="B109" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D109" s="16" t="n">
         <v>829</v>
@@ -7520,10 +7657,10 @@
         <v>25</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C110" s="15" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D110" s="16" t="n">
         <v>46521</v>
@@ -7544,10 +7681,10 @@
         <v>25</v>
       </c>
       <c r="B111" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C111" s="15" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D111" s="16" t="n">
         <v>3644</v>
@@ -7568,10 +7705,10 @@
         <v>25</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D112" s="16" t="n">
         <v>611</v>
@@ -7592,10 +7729,10 @@
         <v>25</v>
       </c>
       <c r="B113" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D113" s="16" t="n">
         <v>9748</v>
@@ -7616,10 +7753,10 @@
         <v>25</v>
       </c>
       <c r="B114" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D114" s="16" t="n">
         <v>3044</v>
@@ -7640,10 +7777,10 @@
         <v>25</v>
       </c>
       <c r="B115" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D115" s="16" t="n">
         <v>2721</v>
@@ -7664,10 +7801,10 @@
         <v>25</v>
       </c>
       <c r="B116" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C116" s="15" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D116" s="16" t="n">
         <v>24594</v>
@@ -7688,10 +7825,10 @@
         <v>25</v>
       </c>
       <c r="B117" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C117" s="15" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D117" s="16" t="n">
         <v>3000</v>
@@ -7712,10 +7849,10 @@
         <v>25</v>
       </c>
       <c r="B118" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D118" s="16" t="n">
         <v>2912</v>
@@ -7736,10 +7873,10 @@
         <v>25</v>
       </c>
       <c r="B119" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C119" s="15" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D119" s="16" t="n">
         <v>13195</v>
@@ -7760,10 +7897,10 @@
         <v>25</v>
       </c>
       <c r="B120" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C120" s="15" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D120" s="16" t="n">
         <v>15287</v>
@@ -7784,10 +7921,10 @@
         <v>25</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D121" s="16" t="n">
         <v>6781</v>
@@ -7808,10 +7945,10 @@
         <v>25</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C122" s="15" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D122" s="16" t="n">
         <v>12594</v>
@@ -7832,10 +7969,10 @@
         <v>25</v>
       </c>
       <c r="B123" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D123" s="16" t="n">
         <v>900</v>
@@ -7856,10 +7993,10 @@
         <v>28</v>
       </c>
       <c r="B124" s="15" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D124" s="16" t="n">
         <v>1060</v>
@@ -7880,10 +8017,10 @@
         <v>28</v>
       </c>
       <c r="B125" s="15" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D125" s="16" t="n">
         <v>700</v>
@@ -7904,10 +8041,10 @@
         <v>28</v>
       </c>
       <c r="B126" s="15" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D126" s="16" t="n">
         <v>19607</v>
@@ -7928,10 +8065,10 @@
         <v>28</v>
       </c>
       <c r="B127" s="15" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D127" s="16" t="n">
         <v>10440</v>
@@ -7952,10 +8089,10 @@
         <v>28</v>
       </c>
       <c r="B128" s="15" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C128" s="15" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D128" s="16" t="n">
         <v>4418</v>
@@ -7976,10 +8113,10 @@
         <v>28</v>
       </c>
       <c r="B129" s="15" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C129" s="15" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D129" s="16" t="n">
         <v>13632</v>
@@ -8000,10 +8137,10 @@
         <v>28</v>
       </c>
       <c r="B130" s="15" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D130" s="16" t="n">
         <v>443</v>
@@ -8024,10 +8161,10 @@
         <v>28</v>
       </c>
       <c r="B131" s="15" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C131" s="15" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D131" s="16" t="n">
         <v>890</v>
@@ -8048,10 +8185,10 @@
         <v>28</v>
       </c>
       <c r="B132" s="15" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C132" s="15" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D132" s="16" t="n">
         <v>9500</v>
@@ -8072,10 +8209,10 @@
         <v>28</v>
       </c>
       <c r="B133" s="15" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C133" s="15" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D133" s="16" t="n">
         <v>12090</v>
@@ -8096,10 +8233,10 @@
         <v>28</v>
       </c>
       <c r="B134" s="15" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C134" s="15" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D134" s="16" t="n">
         <v>10000</v>
@@ -8120,10 +8257,10 @@
         <v>28</v>
       </c>
       <c r="B135" s="15" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C135" s="15" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D135" s="16" t="n">
         <v>3070</v>
@@ -8144,10 +8281,10 @@
         <v>28</v>
       </c>
       <c r="B136" s="15" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C136" s="15" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D136" s="16" t="n">
         <v>2120</v>
@@ -8168,10 +8305,10 @@
         <v>28</v>
       </c>
       <c r="B137" s="15" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C137" s="15" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D137" s="16" t="n">
         <v>1002</v>
@@ -8192,10 +8329,10 @@
         <v>28</v>
       </c>
       <c r="B138" s="15" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C138" s="15" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D138" s="16" t="n">
         <v>10602</v>
@@ -8216,10 +8353,10 @@
         <v>28</v>
       </c>
       <c r="B139" s="15" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C139" s="15" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D139" s="16" t="n">
         <v>455</v>
@@ -8240,10 +8377,10 @@
         <v>28</v>
       </c>
       <c r="B140" s="15" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C140" s="15" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D140" s="16" t="n">
         <v>890</v>
@@ -8264,10 +8401,10 @@
         <v>28</v>
       </c>
       <c r="B141" s="15" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C141" s="15" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D141" s="16" t="n">
         <v>12090</v>
@@ -8288,10 +8425,10 @@
         <v>28</v>
       </c>
       <c r="B142" s="15" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C142" s="15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D142" s="16" t="n">
         <v>1839</v>
@@ -8312,10 +8449,10 @@
         <v>28</v>
       </c>
       <c r="B143" s="15" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C143" s="15" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D143" s="16" t="n">
         <v>627</v>
@@ -8336,10 +8473,10 @@
         <v>28</v>
       </c>
       <c r="B144" s="15" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C144" s="15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D144" s="16" t="n">
         <v>3149</v>
@@ -8360,10 +8497,10 @@
         <v>28</v>
       </c>
       <c r="B145" s="15" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C145" s="15" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D145" s="16" t="n">
         <v>2151</v>
@@ -8384,10 +8521,10 @@
         <v>28</v>
       </c>
       <c r="B146" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C146" s="15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D146" s="16" t="n">
         <v>5863</v>
@@ -8408,10 +8545,10 @@
         <v>28</v>
       </c>
       <c r="B147" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C147" s="15" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D147" s="16" t="n">
         <v>40162</v>
@@ -8432,10 +8569,10 @@
         <v>28</v>
       </c>
       <c r="B148" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C148" s="15" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D148" s="16" t="n">
         <v>812</v>
@@ -8456,10 +8593,10 @@
         <v>28</v>
       </c>
       <c r="B149" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C149" s="15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D149" s="16" t="n">
         <v>4644</v>
@@ -8480,10 +8617,10 @@
         <v>28</v>
       </c>
       <c r="B150" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C150" s="15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D150" s="16" t="n">
         <v>84339</v>
@@ -8504,10 +8641,10 @@
         <v>28</v>
       </c>
       <c r="B151" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C151" s="15" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D151" s="16" t="n">
         <v>26353</v>
@@ -8528,10 +8665,10 @@
         <v>28</v>
       </c>
       <c r="B152" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C152" s="15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D152" s="16" t="n">
         <v>2381</v>
@@ -8550,10 +8687,10 @@
         <v>28</v>
       </c>
       <c r="B153" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C153" s="15" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D153" s="16" t="n">
         <v>48965</v>
@@ -8574,10 +8711,10 @@
         <v>28</v>
       </c>
       <c r="B154" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C154" s="15" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D154" s="16" t="n">
         <v>2187</v>
@@ -8598,10 +8735,10 @@
         <v>28</v>
       </c>
       <c r="B155" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C155" s="15" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D155" s="16" t="n">
         <v>35860</v>
@@ -8622,10 +8759,10 @@
         <v>28</v>
       </c>
       <c r="B156" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C156" s="15" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D156" s="16" t="n">
         <v>47395</v>
@@ -8646,10 +8783,10 @@
         <v>28</v>
       </c>
       <c r="B157" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C157" s="15" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D157" s="16" t="n">
         <v>2226</v>
@@ -8670,10 +8807,10 @@
         <v>28</v>
       </c>
       <c r="B158" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C158" s="15" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D158" s="16" t="n">
         <v>56164</v>
@@ -8694,10 +8831,10 @@
         <v>28</v>
       </c>
       <c r="B159" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C159" s="15" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D159" s="16" t="n">
         <v>32056</v>
@@ -8718,10 +8855,10 @@
         <v>10</v>
       </c>
       <c r="B160" s="15" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C160" s="15" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D160" s="16" t="n">
         <v>88966</v>
@@ -8742,10 +8879,10 @@
         <v>10</v>
       </c>
       <c r="B161" s="15" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C161" s="15" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D161" s="16" t="n">
         <v>172681</v>
@@ -8766,10 +8903,10 @@
         <v>10</v>
       </c>
       <c r="B162" s="15" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C162" s="15" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D162" s="16" t="n">
         <v>130371</v>
@@ -8790,10 +8927,10 @@
         <v>10</v>
       </c>
       <c r="B163" s="15" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D163" s="16" t="n">
         <v>370639</v>
@@ -8814,10 +8951,10 @@
         <v>10</v>
       </c>
       <c r="B164" s="15" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C164" s="15" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D164" s="16" t="n">
         <v>175387</v>
@@ -8838,10 +8975,10 @@
         <v>10</v>
       </c>
       <c r="B165" s="15" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C165" s="15" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D165" s="16" t="n">
         <v>134787</v>
@@ -8862,10 +8999,10 @@
         <v>10</v>
       </c>
       <c r="B166" s="15" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C166" s="15" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D166" s="16" t="n">
         <v>189937</v>
@@ -8886,10 +9023,10 @@
         <v>10</v>
       </c>
       <c r="B167" s="15" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C167" s="15" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D167" s="16" t="n">
         <v>994</v>
@@ -8910,10 +9047,10 @@
         <v>10</v>
       </c>
       <c r="B168" s="15" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C168" s="15" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D168" s="16" t="n">
         <v>160051</v>
@@ -8934,10 +9071,10 @@
         <v>10</v>
       </c>
       <c r="B169" s="15" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C169" s="15" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D169" s="16" t="n">
         <v>13638</v>
@@ -8958,10 +9095,10 @@
         <v>10</v>
       </c>
       <c r="B170" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C170" s="15" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D170" s="16" t="n">
         <v>200411</v>
@@ -8982,10 +9119,10 @@
         <v>10</v>
       </c>
       <c r="B171" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C171" s="15" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D171" s="16" t="n">
         <v>160572</v>
@@ -9006,10 +9143,10 @@
         <v>10</v>
       </c>
       <c r="B172" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C172" s="15" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D172" s="16" t="n">
         <v>200202</v>
@@ -9030,10 +9167,10 @@
         <v>10</v>
       </c>
       <c r="B173" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C173" s="15" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D173" s="16" t="n">
         <v>144941</v>
@@ -9054,10 +9191,10 @@
         <v>10</v>
       </c>
       <c r="B174" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C174" s="15" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D174" s="16" t="n">
         <v>28056</v>
@@ -9078,10 +9215,10 @@
         <v>10</v>
       </c>
       <c r="B175" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C175" s="15" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D175" s="16" t="n">
         <v>167156</v>
@@ -9102,10 +9239,10 @@
         <v>10</v>
       </c>
       <c r="B176" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C176" s="15" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D176" s="16" t="n">
         <v>100919</v>
@@ -9126,10 +9263,10 @@
         <v>10</v>
       </c>
       <c r="B177" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C177" s="15" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D177" s="16" t="n">
         <v>179012</v>
@@ -9150,10 +9287,10 @@
         <v>10</v>
       </c>
       <c r="B178" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C178" s="15" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D178" s="16" t="n">
         <v>207757</v>
@@ -9174,10 +9311,10 @@
         <v>14</v>
       </c>
       <c r="B179" s="15" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C179" s="15" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D179" s="16" t="n">
         <v>1350</v>
@@ -9198,10 +9335,10 @@
         <v>14</v>
       </c>
       <c r="B180" s="15" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C180" s="15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D180" s="16" t="n">
         <v>1969</v>
@@ -9222,10 +9359,10 @@
         <v>14</v>
       </c>
       <c r="B181" s="15" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C181" s="15" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D181" s="16" t="n">
         <v>1138</v>
@@ -9246,10 +9383,10 @@
         <v>14</v>
       </c>
       <c r="B182" s="15" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C182" s="15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D182" s="16" t="n">
         <v>3963</v>
@@ -9270,10 +9407,10 @@
         <v>14</v>
       </c>
       <c r="B183" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C183" s="15" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D183" s="16" t="n">
         <v>6361</v>
@@ -9294,10 +9431,10 @@
         <v>14</v>
       </c>
       <c r="B184" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C184" s="15" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D184" s="16" t="n">
         <v>2297</v>
@@ -9318,10 +9455,10 @@
         <v>14</v>
       </c>
       <c r="B185" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C185" s="15" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D185" s="16" t="n">
         <v>3824</v>
@@ -9342,10 +9479,10 @@
         <v>14</v>
       </c>
       <c r="B186" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C186" s="15" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D186" s="16" t="n">
         <v>3823</v>
@@ -9366,10 +9503,10 @@
         <v>14</v>
       </c>
       <c r="B187" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C187" s="15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D187" s="16" t="n">
         <v>20545</v>
@@ -9390,10 +9527,10 @@
         <v>14</v>
       </c>
       <c r="B188" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C188" s="15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D188" s="16" t="n">
         <v>15631</v>
@@ -9414,10 +9551,10 @@
         <v>14</v>
       </c>
       <c r="B189" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C189" s="15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D189" s="16" t="n">
         <v>18775</v>
@@ -9438,10 +9575,10 @@
         <v>14</v>
       </c>
       <c r="B190" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C190" s="15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D190" s="16" t="n">
         <v>22139</v>
@@ -9459,13 +9596,13 @@
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="15" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B191" s="15" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C191" s="15" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D191" s="16" t="n">
         <v>23182</v>
@@ -9483,13 +9620,13 @@
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="15" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B192" s="15" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C192" s="15" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D192" s="16" t="n">
         <v>2223</v>
@@ -9507,13 +9644,13 @@
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="15" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B193" s="15" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C193" s="15" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D193" s="16" t="n">
         <v>19732</v>
@@ -9531,13 +9668,13 @@
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B194" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C194" s="15" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D194" s="16" t="n">
         <v>50</v>
@@ -9555,13 +9692,13 @@
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B195" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C195" s="15" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D195" s="16" t="n">
         <v>500</v>
@@ -9579,13 +9716,13 @@
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B196" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C196" s="15" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D196" s="16" t="n">
         <v>3892</v>
@@ -9603,13 +9740,13 @@
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B197" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C197" s="15" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D197" s="16" t="n">
         <v>3373</v>
@@ -9627,13 +9764,13 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B198" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C198" s="15" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D198" s="16" t="n">
         <v>3813</v>
@@ -9651,13 +9788,13 @@
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B199" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C199" s="15" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D199" s="16" t="n">
         <v>290</v>
@@ -9675,13 +9812,13 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B200" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C200" s="15" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D200" s="16" t="n">
         <v>2061</v>
@@ -9699,13 +9836,13 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B201" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C201" s="15" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D201" s="16" t="n">
         <v>6</v>
@@ -9723,13 +9860,13 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B202" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C202" s="15" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D202" s="16" t="n">
         <v>1099</v>
@@ -9747,13 +9884,13 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B203" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C203" s="15" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D203" s="16" t="n">
         <v>300</v>
@@ -9771,13 +9908,13 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B204" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C204" s="15" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D204" s="16" t="n">
         <v>1916</v>
@@ -9795,13 +9932,13 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B205" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C205" s="15" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D205" s="16" t="n">
         <v>52</v>
@@ -9819,13 +9956,13 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B206" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C206" s="15" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D206" s="16" t="n">
         <v>9386</v>
@@ -9843,13 +9980,13 @@
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B207" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C207" s="15" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D207" s="16" t="n">
         <v>298</v>
@@ -9867,13 +10004,13 @@
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B208" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C208" s="15" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D208" s="16" t="n">
         <v>20689</v>
@@ -9888,18 +10025,18 @@
         <v>366</v>
       </c>
       <c r="H208" s="15" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B209" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C209" s="15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D209" s="16" t="n">
         <v>27289</v>
@@ -9914,18 +10051,18 @@
         <v>511</v>
       </c>
       <c r="H209" s="15" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B210" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C210" s="15" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D210" s="16" t="n">
         <v>200</v>
@@ -9943,13 +10080,13 @@
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B211" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C211" s="15" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D211" s="16" t="n">
         <v>2582</v>
@@ -9967,13 +10104,13 @@
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B212" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C212" s="15" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D212" s="16" t="n">
         <v>11323</v>
@@ -9991,13 +10128,13 @@
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B213" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C213" s="15" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D213" s="16" t="n">
         <v>811</v>
@@ -10015,13 +10152,13 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B214" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C214" s="15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D214" s="16" t="n">
         <v>14305</v>
@@ -10039,13 +10176,13 @@
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="15" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B215" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C215" s="15" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D215" s="16" t="n">
         <v>2675</v>
@@ -10063,13 +10200,13 @@
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="15" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B216" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C216" s="15" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D216" s="16" t="n">
         <v>500</v>
@@ -10087,13 +10224,13 @@
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="15" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B217" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C217" s="15" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D217" s="16" t="n">
         <v>384</v>
@@ -10108,18 +10245,18 @@
         <v>768</v>
       </c>
       <c r="H217" s="15" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="15" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B218" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C218" s="15" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D218" s="16" t="n">
         <v>10000</v>
@@ -10137,13 +10274,13 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="15" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B219" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C219" s="15" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D219" s="16" t="n">
         <v>887</v>
@@ -10161,13 +10298,13 @@
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="15" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B220" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C220" s="15" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D220" s="16" t="n">
         <v>1046</v>
@@ -10185,13 +10322,13 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="15" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B221" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C221" s="15" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D221" s="16" t="n">
         <v>311</v>
@@ -10239,25 +10376,25 @@
         <v>2</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>33</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>5</v>
@@ -10268,13 +10405,13 @@
         <v>10</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E2" s="16" t="n">
         <v>18</v>
@@ -10295,13 +10432,13 @@
         <v>10</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E3" s="16" t="n">
         <v>55</v>
@@ -10322,13 +10459,13 @@
         <v>10</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E4" s="16" t="n">
         <v>109</v>
@@ -10349,13 +10486,13 @@
         <v>10</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E5" s="16" t="n">
         <v>16</v>
@@ -10376,13 +10513,13 @@
         <v>10</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E6" s="16" t="n">
         <v>18</v>
@@ -10403,13 +10540,13 @@
         <v>10</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E7" s="16" t="n">
         <v>52</v>
@@ -10428,13 +10565,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E8" s="16" t="n">
         <v>18</v>
@@ -10455,13 +10592,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E9" s="16" t="n">
         <v>15</v>
@@ -10482,13 +10619,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="C10" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C10" s="15" t="s">
-        <v>123</v>
-      </c>
       <c r="D10" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E10" s="16" t="n">
         <v>2</v>
@@ -10509,13 +10646,13 @@
         <v>6</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E11" s="16" t="n">
         <v>54</v>
@@ -10536,13 +10673,13 @@
         <v>6</v>
       </c>
       <c r="B12" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C12" s="15" t="s">
-        <v>123</v>
-      </c>
       <c r="D12" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E12" s="16" t="n">
         <v>8</v>
@@ -10563,13 +10700,13 @@
         <v>6</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E13" s="16" t="n">
         <v>18</v>
@@ -10590,13 +10727,13 @@
         <v>6</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E14" s="16" t="n">
         <v>1</v>
@@ -10617,13 +10754,13 @@
         <v>6</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E15" s="16" t="n">
         <v>2</v>
@@ -10642,13 +10779,13 @@
         <v>6</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E16" s="16" t="n">
         <v>7</v>
@@ -10669,13 +10806,13 @@
         <v>6</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E17" s="16" t="n">
         <v>71</v>
@@ -10696,13 +10833,13 @@
         <v>6</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E18" s="16" t="n">
         <v>60</v>
@@ -10723,13 +10860,13 @@
         <v>6</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E19" s="16" t="n">
         <v>15</v>
@@ -10750,13 +10887,13 @@
         <v>6</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E20" s="16" t="n">
         <v>1</v>
@@ -10775,13 +10912,13 @@
         <v>6</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E21" s="16" t="n">
         <v>10</v>
@@ -10802,13 +10939,13 @@
         <v>6</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E22" s="16" t="n">
         <v>1</v>
@@ -10829,13 +10966,13 @@
         <v>6</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E23" s="16" t="n">
         <v>78</v>
@@ -10856,13 +10993,13 @@
         <v>6</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E24" s="16" t="n">
         <v>54</v>
@@ -10883,13 +11020,13 @@
         <v>6</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E25" s="16" t="n">
         <v>6</v>
@@ -10910,13 +11047,13 @@
         <v>6</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E26" s="16" t="n">
         <v>25</v>
@@ -10937,13 +11074,13 @@
         <v>6</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E27" s="16" t="n">
         <v>31</v>
@@ -10964,13 +11101,13 @@
         <v>6</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E28" s="16" t="n">
         <v>63</v>
@@ -10991,13 +11128,13 @@
         <v>6</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E29" s="16" t="n">
         <v>56</v>
@@ -11018,13 +11155,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E30" s="16" t="n">
         <v>5</v>
@@ -11045,13 +11182,13 @@
         <v>6</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E31" s="16" t="n">
         <v>26</v>
@@ -11072,13 +11209,13 @@
         <v>6</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E32" s="16" t="n">
         <v>65</v>
@@ -11099,13 +11236,13 @@
         <v>6</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E33" s="16" t="n">
         <v>3</v>
@@ -11126,13 +11263,13 @@
         <v>6</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E34" s="16" t="n">
         <v>99</v>
@@ -11153,13 +11290,13 @@
         <v>6</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E35" s="16" t="n">
         <v>139</v>
@@ -11180,13 +11317,13 @@
         <v>6</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E36" s="16" t="n">
         <v>7</v>
@@ -11207,13 +11344,13 @@
         <v>6</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E37" s="16" t="n">
         <v>7</v>
@@ -11234,13 +11371,13 @@
         <v>6</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C38" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="D38" s="15" t="s">
         <v>181</v>
-      </c>
-      <c r="D38" s="15" t="s">
-        <v>178</v>
       </c>
       <c r="E38" s="16" t="n">
         <v>2</v>
@@ -11261,13 +11398,13 @@
         <v>6</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E39" s="16" t="n">
         <v>25</v>
@@ -11288,13 +11425,13 @@
         <v>6</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E40" s="16" t="n">
         <v>30</v>
@@ -11315,13 +11452,13 @@
         <v>6</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E41" s="16" t="n">
         <v>52</v>
@@ -11342,13 +11479,13 @@
         <v>6</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E42" s="16" t="n">
         <v>23</v>
@@ -11369,13 +11506,13 @@
         <v>6</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E43" s="16" t="n">
         <v>47</v>
@@ -11390,7 +11527,7 @@
         <v>141</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11398,13 +11535,13 @@
         <v>6</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E44" s="16" t="n">
         <v>39</v>
@@ -11425,13 +11562,13 @@
         <v>6</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E45" s="16" t="n">
         <v>120</v>
@@ -11452,13 +11589,13 @@
         <v>6</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E46" s="16" t="n">
         <v>2</v>
@@ -11477,13 +11614,13 @@
         <v>6</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E47" s="16" t="n">
         <v>45</v>
@@ -11496,7 +11633,7 @@
         <v>45</v>
       </c>
       <c r="I47" s="17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11504,13 +11641,13 @@
         <v>6</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E48" s="16" t="n">
         <v>13</v>
@@ -11529,13 +11666,13 @@
         <v>6</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E49" s="16" t="n">
         <v>132</v>
@@ -11554,13 +11691,13 @@
         <v>25</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E50" s="16" t="n">
         <v>9</v>
@@ -11581,13 +11718,13 @@
         <v>25</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E51" s="16" t="n">
         <v>4</v>
@@ -11608,13 +11745,13 @@
         <v>25</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E52" s="16" t="n">
         <v>8</v>
@@ -11635,13 +11772,13 @@
         <v>25</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E53" s="16" t="n">
         <v>21</v>
@@ -11662,13 +11799,13 @@
         <v>25</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E54" s="16" t="n">
         <v>138</v>
@@ -11689,13 +11826,13 @@
         <v>25</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E55" s="16" t="n">
         <v>88</v>
@@ -11716,13 +11853,13 @@
         <v>25</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E56" s="16" t="n">
         <v>5</v>
@@ -11743,13 +11880,13 @@
         <v>25</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E57" s="16" t="n">
         <v>66</v>
@@ -11770,13 +11907,13 @@
         <v>25</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E58" s="16" t="n">
         <v>15</v>
@@ -11797,13 +11934,13 @@
         <v>25</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E59" s="16" t="n">
         <v>122</v>
@@ -11824,13 +11961,13 @@
         <v>25</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E60" s="16" t="n">
         <v>6</v>
@@ -11851,13 +11988,13 @@
         <v>25</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E61" s="16" t="n">
         <v>6</v>
@@ -11872,7 +12009,7 @@
         <v>24</v>
       </c>
       <c r="I61" s="15" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11880,13 +12017,13 @@
         <v>25</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E62" s="16" t="n">
         <v>2</v>
@@ -11907,13 +12044,13 @@
         <v>25</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E63" s="16" t="n">
         <v>20</v>
@@ -11934,13 +12071,13 @@
         <v>25</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E64" s="16" t="n">
         <v>26</v>
@@ -11961,13 +12098,13 @@
         <v>25</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E65" s="16" t="n">
         <v>36</v>
@@ -11988,13 +12125,13 @@
         <v>25</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E66" s="16" t="n">
         <v>143</v>
@@ -12015,13 +12152,13 @@
         <v>25</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E67" s="16" t="n">
         <v>6</v>
@@ -12042,13 +12179,13 @@
         <v>25</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E68" s="16" t="n">
         <v>21</v>
@@ -12069,13 +12206,13 @@
         <v>25</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E69" s="16" t="n">
         <v>29</v>
@@ -12096,13 +12233,13 @@
         <v>25</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E70" s="16" t="n">
         <v>133</v>
@@ -12123,13 +12260,13 @@
         <v>25</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E71" s="16" t="n">
         <v>2</v>
@@ -12150,13 +12287,13 @@
         <v>25</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E72" s="16" t="n">
         <v>4</v>
@@ -12177,13 +12314,13 @@
         <v>25</v>
       </c>
       <c r="B73" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C73" s="15" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E73" s="16" t="n">
         <v>20</v>
@@ -12204,13 +12341,13 @@
         <v>25</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E74" s="16" t="n">
         <v>34</v>
@@ -12231,13 +12368,13 @@
         <v>25</v>
       </c>
       <c r="B75" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E75" s="16" t="n">
         <v>57</v>
@@ -12256,13 +12393,13 @@
         <v>25</v>
       </c>
       <c r="B76" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C76" s="15" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E76" s="16" t="n">
         <v>6</v>
@@ -12283,13 +12420,13 @@
         <v>25</v>
       </c>
       <c r="B77" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D77" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E77" s="16" t="n">
         <v>6</v>
@@ -12310,13 +12447,13 @@
         <v>25</v>
       </c>
       <c r="B78" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C78" s="15" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D78" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E78" s="16" t="n">
         <v>21</v>
@@ -12337,13 +12474,13 @@
         <v>25</v>
       </c>
       <c r="B79" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E79" s="16" t="n">
         <v>16</v>
@@ -12364,13 +12501,13 @@
         <v>25</v>
       </c>
       <c r="B80" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D80" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E80" s="16" t="n">
         <v>10</v>
@@ -12391,13 +12528,13 @@
         <v>25</v>
       </c>
       <c r="B81" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E81" s="16" t="n">
         <v>23</v>
@@ -12416,13 +12553,13 @@
         <v>25</v>
       </c>
       <c r="B82" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D82" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E82" s="16" t="n">
         <v>3</v>
@@ -12441,13 +12578,13 @@
         <v>25</v>
       </c>
       <c r="B83" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E83" s="16" t="n">
         <v>16</v>
@@ -12466,13 +12603,13 @@
         <v>25</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D84" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E84" s="16" t="n">
         <v>81</v>
@@ -12491,13 +12628,13 @@
         <v>25</v>
       </c>
       <c r="B85" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E85" s="16" t="n">
         <v>2</v>
@@ -12516,13 +12653,13 @@
         <v>25</v>
       </c>
       <c r="B86" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D86" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E86" s="16" t="n">
         <v>157</v>
@@ -12541,13 +12678,13 @@
         <v>28</v>
       </c>
       <c r="B87" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E87" s="16" t="n">
         <v>1</v>
@@ -12566,13 +12703,13 @@
         <v>28</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D88" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E88" s="16" t="n">
         <v>19</v>
@@ -12593,13 +12730,13 @@
         <v>28</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D89" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E89" s="16" t="n">
         <v>11</v>
@@ -12620,13 +12757,13 @@
         <v>28</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D90" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E90" s="16" t="n">
         <v>14</v>
@@ -12647,13 +12784,13 @@
         <v>28</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D91" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E91" s="16" t="n">
         <v>3</v>
@@ -12674,13 +12811,13 @@
         <v>28</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D92" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E92" s="16" t="n">
         <v>11</v>
@@ -12701,13 +12838,13 @@
         <v>28</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D93" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E93" s="16" t="n">
         <v>25</v>
@@ -12728,13 +12865,13 @@
         <v>28</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D94" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E94" s="16" t="n">
         <v>11</v>
@@ -12755,13 +12892,13 @@
         <v>28</v>
       </c>
       <c r="B95" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C95" s="15" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D95" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E95" s="16" t="n">
         <v>19</v>
@@ -12782,13 +12919,13 @@
         <v>28</v>
       </c>
       <c r="B96" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D96" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E96" s="16" t="n">
         <v>38</v>
@@ -12809,13 +12946,13 @@
         <v>28</v>
       </c>
       <c r="B97" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D97" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E97" s="16" t="n">
         <v>16</v>
@@ -12830,7 +12967,7 @@
         <v>32</v>
       </c>
       <c r="I97" s="15" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12838,13 +12975,13 @@
         <v>28</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D98" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E98" s="16" t="n">
         <v>262</v>
@@ -12865,13 +13002,13 @@
         <v>28</v>
       </c>
       <c r="B99" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D99" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E99" s="16" t="n">
         <v>1</v>
@@ -12890,13 +13027,13 @@
         <v>28</v>
       </c>
       <c r="B100" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D100" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E100" s="16" t="n">
         <v>3</v>
@@ -12917,13 +13054,13 @@
         <v>28</v>
       </c>
       <c r="B101" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C101" s="15" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D101" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E101" s="16" t="n">
         <v>3</v>
@@ -12938,7 +13075,7 @@
         <v>9</v>
       </c>
       <c r="I101" s="15" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12946,13 +13083,13 @@
         <v>28</v>
       </c>
       <c r="B102" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D102" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E102" s="16" t="n">
         <v>35</v>
@@ -12967,7 +13104,7 @@
         <v>70</v>
       </c>
       <c r="I102" s="15" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12975,13 +13112,13 @@
         <v>28</v>
       </c>
       <c r="B103" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C103" s="15" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D103" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E103" s="16" t="n">
         <v>46</v>
@@ -13002,13 +13139,13 @@
         <v>28</v>
       </c>
       <c r="B104" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C104" s="15" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D104" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E104" s="16" t="n">
         <v>3</v>
@@ -13023,7 +13160,7 @@
         <v>12</v>
       </c>
       <c r="I104" s="15" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13031,13 +13168,13 @@
         <v>28</v>
       </c>
       <c r="B105" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C105" s="15" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D105" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E105" s="16" t="n">
         <v>18</v>
@@ -13052,7 +13189,7 @@
         <v>54</v>
       </c>
       <c r="I105" s="15" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13060,13 +13197,13 @@
         <v>28</v>
       </c>
       <c r="B106" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D106" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E106" s="16" t="n">
         <v>146</v>
@@ -13087,13 +13224,13 @@
         <v>28</v>
       </c>
       <c r="B107" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C107" s="15" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D107" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E107" s="16" t="n">
         <v>89</v>
@@ -13114,13 +13251,13 @@
         <v>28</v>
       </c>
       <c r="B108" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C108" s="15" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D108" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E108" s="16" t="n">
         <v>49</v>
@@ -13139,13 +13276,13 @@
         <v>14</v>
       </c>
       <c r="B109" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D109" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E109" s="16" t="n">
         <v>4</v>
@@ -13166,13 +13303,13 @@
         <v>14</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C110" s="15" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D110" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E110" s="16" t="n">
         <v>157</v>
@@ -13193,13 +13330,13 @@
         <v>14</v>
       </c>
       <c r="B111" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C111" s="15" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D111" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E111" s="16" t="n">
         <v>145</v>
@@ -13220,13 +13357,13 @@
         <v>14</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D112" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E112" s="16" t="n">
         <v>229</v>
@@ -13247,13 +13384,13 @@
         <v>14</v>
       </c>
       <c r="B113" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D113" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E113" s="16" t="n">
         <v>50</v>
@@ -13274,13 +13411,13 @@
         <v>14</v>
       </c>
       <c r="B114" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D114" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E114" s="16" t="n">
         <v>281</v>
@@ -13301,13 +13438,13 @@
         <v>14</v>
       </c>
       <c r="B115" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D115" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E115" s="16" t="n">
         <v>39</v>
@@ -13328,13 +13465,13 @@
         <v>14</v>
       </c>
       <c r="B116" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C116" s="15" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D116" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E116" s="16" t="n">
         <v>279</v>
@@ -13355,13 +13492,13 @@
         <v>14</v>
       </c>
       <c r="B117" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C117" s="15" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D117" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E117" s="16" t="n">
         <v>93</v>
@@ -13382,13 +13519,13 @@
         <v>14</v>
       </c>
       <c r="B118" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D118" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E118" s="16" t="n">
         <v>567</v>
@@ -13409,13 +13546,13 @@
         <v>14</v>
       </c>
       <c r="B119" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C119" s="15" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D119" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E119" s="16" t="n">
         <v>46</v>
@@ -13436,13 +13573,13 @@
         <v>14</v>
       </c>
       <c r="B120" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C120" s="15" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D120" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E120" s="16" t="n">
         <v>273</v>
@@ -13463,13 +13600,13 @@
         <v>14</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D121" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E121" s="16" t="n">
         <v>86</v>
@@ -13490,13 +13627,13 @@
         <v>14</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C122" s="15" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D122" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E122" s="16" t="n">
         <v>480</v>
@@ -13517,13 +13654,13 @@
         <v>14</v>
       </c>
       <c r="B123" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D123" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E123" s="16" t="n">
         <v>11</v>
@@ -13541,16 +13678,16 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B124" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D124" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E124" s="16" t="n">
         <v>1</v>
@@ -13566,16 +13703,16 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B125" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D125" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E125" s="16" t="n">
         <v>10</v>
@@ -13593,16 +13730,16 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B126" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D126" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E126" s="16" t="n">
         <v>78</v>
@@ -13618,16 +13755,16 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B127" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D127" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E127" s="16" t="n">
         <v>15</v>
@@ -13642,21 +13779,21 @@
         <v>60</v>
       </c>
       <c r="I127" s="15" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B128" s="15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C128" s="15" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D128" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E128" s="16" t="n">
         <v>5</v>
@@ -13672,16 +13809,16 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B129" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C129" s="15" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D129" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E129" s="16" t="n">
         <v>11</v>
@@ -13699,16 +13836,16 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B130" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D130" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E130" s="16" t="n">
         <v>8</v>
@@ -13726,16 +13863,16 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B131" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C131" s="15" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D131" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E131" s="16" t="n">
         <v>1</v>
@@ -13753,16 +13890,16 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B132" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C132" s="15" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D132" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E132" s="16" t="n">
         <v>43</v>
@@ -13780,16 +13917,16 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B133" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C133" s="15" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D133" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E133" s="16" t="n">
         <v>4</v>
@@ -13807,16 +13944,16 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B134" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C134" s="15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D134" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E134" s="16" t="n">
         <v>248</v>
@@ -13831,21 +13968,21 @@
         <v>744</v>
       </c>
       <c r="I134" s="15" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B135" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C135" s="15" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D135" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E135" s="16" t="n">
         <v>46</v>
@@ -13863,16 +14000,16 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B136" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C136" s="15" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D136" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E136" s="16" t="n">
         <v>5</v>
@@ -13890,16 +14027,16 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B137" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C137" s="15" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D137" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E137" s="16" t="n">
         <v>1</v>
@@ -13917,16 +14054,16 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B138" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C138" s="15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D138" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E138" s="16" t="n">
         <v>18</v>
@@ -13944,16 +14081,16 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B139" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C139" s="15" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D139" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E139" s="16" t="n">
         <v>9</v>
@@ -13971,16 +14108,16 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B140" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C140" s="15" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D140" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E140" s="16" t="n">
         <v>7</v>
@@ -13998,16 +14135,16 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B141" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C141" s="15" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D141" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E141" s="16" t="n">
         <v>34</v>
@@ -14025,16 +14162,16 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B142" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C142" s="15" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D142" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E142" s="16" t="n">
         <v>2</v>
@@ -14052,16 +14189,16 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B143" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C143" s="15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D143" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E143" s="16" t="n">
         <v>250</v>
@@ -14079,16 +14216,16 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B144" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C144" s="15" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D144" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E144" s="16" t="n">
         <v>146</v>
@@ -14106,16 +14243,16 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B145" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C145" s="15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D145" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E145" s="16" t="n">
         <v>12</v>
@@ -14133,16 +14270,16 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B146" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C146" s="15" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D146" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E146" s="16" t="n">
         <v>9</v>
@@ -14160,16 +14297,16 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B147" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C147" s="15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D147" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E147" s="16" t="n">
         <v>150</v>
@@ -14187,16 +14324,16 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B148" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C148" s="15" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D148" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E148" s="16" t="n">
         <v>86</v>
@@ -14214,16 +14351,16 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B149" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C149" s="15" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D149" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E149" s="16" t="n">
         <v>25</v>
@@ -14241,16 +14378,16 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B150" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C150" s="15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D150" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E150" s="16" t="n">
         <v>52</v>
@@ -14268,16 +14405,16 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B151" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C151" s="15" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D151" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E151" s="16" t="n">
         <v>6</v>
@@ -14295,16 +14432,16 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B152" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C152" s="15" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D152" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E152" s="16" t="n">
         <v>11</v>
@@ -14322,16 +14459,16 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B153" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C153" s="15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D153" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E153" s="16" t="n">
         <v>194</v>
@@ -14349,16 +14486,16 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B154" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C154" s="15" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D154" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E154" s="16" t="n">
         <v>46</v>
@@ -14376,16 +14513,16 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B155" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C155" s="15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D155" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E155" s="16" t="n">
         <v>33</v>
@@ -14403,16 +14540,16 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B156" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C156" s="15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D156" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E156" s="16" t="n">
         <v>67</v>
@@ -14430,16 +14567,16 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="15" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B157" s="15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C157" s="15" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D157" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E157" s="16" t="n">
         <v>8</v>
@@ -14457,16 +14594,16 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="15" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B158" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C158" s="15" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D158" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E158" s="16" t="n">
         <v>31</v>
@@ -14484,16 +14621,16 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="15" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B159" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C159" s="15" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D159" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E159" s="16" t="n">
         <v>82</v>
@@ -14511,16 +14648,16 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="15" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B160" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C160" s="15" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D160" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E160" s="16" t="n">
         <v>16</v>
@@ -14538,16 +14675,16 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="15" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B161" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C161" s="15" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D161" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E161" s="16" t="n">
         <v>8</v>
@@ -14565,16 +14702,16 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="15" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B162" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C162" s="15" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D162" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E162" s="16" t="n">
         <v>24</v>
@@ -14592,16 +14729,16 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="15" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B163" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D163" s="15" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E163" s="16" t="n">
         <v>47</v>
@@ -14619,16 +14756,16 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="15" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B164" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C164" s="15" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D164" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E164" s="16" t="n">
         <v>293</v>
@@ -14676,28 +14813,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>6</v>
@@ -14721,34 +14858,34 @@
         <v>18</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14756,19 +14893,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="7" t="n">
@@ -14802,19 +14939,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
@@ -14844,19 +14981,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>0.01</v>
@@ -14890,19 +15027,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>0.07</v>
@@ -14936,17 +15073,17 @@
         <v>5</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E6" s="15"/>
       <c r="F6" s="17" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>0.02</v>
@@ -14980,17 +15117,17 @@
         <v>6</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E7" s="15"/>
       <c r="F7" s="17" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>0.02</v>
@@ -15024,17 +15161,17 @@
         <v>7</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="17" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>0.02</v>
@@ -15068,19 +15205,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="7" t="n">
@@ -15114,17 +15251,17 @@
         <v>9</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E10" s="15"/>
       <c r="F10" s="17" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>0.01</v>
@@ -15160,19 +15297,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>0.02</v>
@@ -15210,19 +15347,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>0.05</v>
@@ -15266,19 +15403,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D13" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>243</v>
+      </c>
+      <c r="F13" s="17" t="s">
         <v>239</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>240</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>236</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>0.05</v>
@@ -15312,19 +15449,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
@@ -15356,19 +15493,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
@@ -15400,19 +15537,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
@@ -15444,19 +15581,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
@@ -15488,19 +15625,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
@@ -15532,19 +15669,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>0.02</v>
@@ -15578,19 +15715,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="7" t="n">
@@ -15636,19 +15773,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>0.02</v>
@@ -15682,19 +15819,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D22" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>267</v>
+      </c>
+      <c r="F22" s="17" t="s">
         <v>263</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>264</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>260</v>
       </c>
       <c r="G22" s="7"/>
       <c r="H22" s="7" t="n">
@@ -15740,19 +15877,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>0.02</v>
@@ -15794,19 +15931,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
@@ -15852,19 +15989,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>0.02</v>
@@ -15910,19 +16047,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>0.01</v>
@@ -15970,19 +16107,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F27" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G27" s="7"/>
       <c r="H27" s="7"/>
@@ -16026,19 +16163,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
@@ -16084,19 +16221,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
@@ -16140,19 +16277,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F30" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
@@ -16196,19 +16333,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="G31" s="7"/>
       <c r="H31" s="7"/>
@@ -16242,19 +16379,19 @@
         <v>31</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>0.01</v>
@@ -16292,19 +16429,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
@@ -16340,19 +16477,19 @@
         <v>33</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F34" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G34" s="7"/>
       <c r="H34" s="7"/>
@@ -16384,19 +16521,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
@@ -16440,19 +16577,19 @@
         <v>35</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F36" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
@@ -16484,19 +16621,19 @@
         <v>36</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F37" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G37" s="7"/>
       <c r="H37" s="7"/>
@@ -16528,19 +16665,19 @@
         <v>37</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F38" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
@@ -16576,19 +16713,19 @@
         <v>38</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F39" s="17" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>0.01</v>
@@ -16622,19 +16759,19 @@
         <v>39</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F40" s="17" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
@@ -16682,19 +16819,19 @@
         <v>40</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F41" s="17" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
@@ -16738,19 +16875,19 @@
         <v>41</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G42" s="7"/>
       <c r="H42" s="7"/>
@@ -16794,19 +16931,19 @@
         <v>42</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F43" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G43" s="7"/>
       <c r="H43" s="7"/>
@@ -16850,19 +16987,19 @@
         <v>43</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E44" s="17" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F44" s="17" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
@@ -16906,19 +17043,19 @@
         <v>44</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E45" s="17" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F45" s="17" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="G45" s="7"/>
       <c r="H45" s="7"/>
@@ -16962,19 +17099,19 @@
         <v>45</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F46" s="17" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G46" s="7"/>
       <c r="H46" s="7"/>
@@ -17024,19 +17161,19 @@
         <v>46</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F47" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G47" s="7"/>
       <c r="H47" s="7"/>
@@ -17070,19 +17207,19 @@
         <v>47</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F48" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G48" s="7"/>
       <c r="H48" s="7"/>
@@ -17116,19 +17253,19 @@
         <v>48</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F49" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G49" s="7"/>
       <c r="H49" s="7"/>
@@ -17162,19 +17299,19 @@
         <v>49</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F50" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
@@ -17218,19 +17355,19 @@
         <v>50</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F51" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G51" s="7"/>
       <c r="H51" s="7"/>
@@ -17276,19 +17413,19 @@
         <v>51</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F52" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G52" s="7"/>
       <c r="H52" s="7"/>
@@ -17334,19 +17471,19 @@
         <v>52</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F53" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G53" s="7"/>
       <c r="H53" s="7"/>
@@ -17390,19 +17527,19 @@
         <v>53</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F54" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
@@ -17446,19 +17583,19 @@
         <v>54</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F55" s="17" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="G55" s="7" t="n">
         <v>0.02</v>
@@ -17516,19 +17653,19 @@
         <v>55</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F56" s="17" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
@@ -17572,19 +17709,19 @@
         <v>56</v>
       </c>
       <c r="B57" s="17" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F57" s="17" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="7"/>
@@ -17628,19 +17765,19 @@
         <v>57</v>
       </c>
       <c r="B58" s="17" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E58" s="17" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F58" s="17" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G58" s="7"/>
       <c r="H58" s="7"/>
@@ -17684,19 +17821,19 @@
         <v>58</v>
       </c>
       <c r="B59" s="17" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C59" s="17" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D59" s="17" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E59" s="17" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F59" s="17" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G59" s="7" t="n">
         <v>0.01</v>
@@ -17746,19 +17883,19 @@
         <v>59</v>
       </c>
       <c r="B60" s="17" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D60" s="17" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F60" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
@@ -17802,19 +17939,19 @@
         <v>60</v>
       </c>
       <c r="B61" s="17" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F61" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G61" s="7"/>
       <c r="H61" s="7"/>
@@ -17860,19 +17997,19 @@
         <v>61</v>
       </c>
       <c r="B62" s="17" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E62" s="17" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F62" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G62" s="7"/>
       <c r="H62" s="7"/>
@@ -17916,19 +18053,19 @@
         <v>62</v>
       </c>
       <c r="B63" s="17" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E63" s="17" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F63" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
@@ -17962,19 +18099,19 @@
         <v>63</v>
       </c>
       <c r="B64" s="17" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E64" s="17" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F64" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G64" s="7" t="n">
         <v>0.1</v>
@@ -18008,19 +18145,19 @@
         <v>64</v>
       </c>
       <c r="B65" s="17" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D65" s="17" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E65" s="17" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F65" s="17" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="G65" s="7" t="n">
         <v>0.02</v>
@@ -18062,19 +18199,19 @@
         <v>65</v>
       </c>
       <c r="B66" s="17" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C66" s="17" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E66" s="17" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F66" s="17" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G66" s="7" t="n">
         <v>0.01</v>
@@ -18118,19 +18255,19 @@
         <v>66</v>
       </c>
       <c r="B67" s="17" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C67" s="17" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E67" s="17" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F67" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G67" s="7"/>
       <c r="H67" s="7"/>
@@ -18168,19 +18305,19 @@
         <v>67</v>
       </c>
       <c r="B68" s="17" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C68" s="17" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D68" s="17" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E68" s="17" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F68" s="17" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="G68" s="7"/>
       <c r="H68" s="7"/>
@@ -18220,19 +18357,19 @@
         <v>68</v>
       </c>
       <c r="B69" s="17" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C69" s="17" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D69" s="17" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E69" s="17" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F69" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G69" s="7"/>
       <c r="H69" s="7"/>
@@ -18272,19 +18409,19 @@
         <v>69</v>
       </c>
       <c r="B70" s="17" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C70" s="17" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D70" s="17" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E70" s="17" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F70" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
@@ -18324,19 +18461,19 @@
         <v>70</v>
       </c>
       <c r="B71" s="17" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C71" s="17" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D71" s="17" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E71" s="17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="F71" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="7"/>
@@ -18376,19 +18513,19 @@
         <v>71</v>
       </c>
       <c r="B72" s="17" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C72" s="17" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D72" s="17" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E72" s="17" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F72" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G72" s="7"/>
       <c r="H72" s="7"/>
@@ -18432,19 +18569,19 @@
         <v>72</v>
       </c>
       <c r="B73" s="17" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C73" s="17" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D73" s="17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E73" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F73" s="17" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="G73" s="7"/>
       <c r="H73" s="7"/>
@@ -18484,19 +18621,19 @@
         <v>73</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D74" s="17" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E74" s="17" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F74" s="17" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="7"/>
@@ -18536,19 +18673,19 @@
         <v>74</v>
       </c>
       <c r="B75" s="17" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C75" s="17" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D75" s="17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E75" s="17" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F75" s="17" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G75" s="7" t="n">
         <v>0.01</v>
@@ -18596,19 +18733,19 @@
         <v>75</v>
       </c>
       <c r="B76" s="17" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C76" s="17" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="E76" s="17" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="F76" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G76" s="7"/>
       <c r="H76" s="7"/>
@@ -18640,19 +18777,19 @@
         <v>76</v>
       </c>
       <c r="B77" s="17" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C77" s="17" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D77" s="17" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E77" s="17" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="F77" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G77" s="7"/>
       <c r="H77" s="7"/>
@@ -18684,19 +18821,19 @@
         <v>77</v>
       </c>
       <c r="B78" s="17" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C78" s="17" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D78" s="17" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E78" s="17" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F78" s="17" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G78" s="7" t="n">
         <v>0.01</v>
@@ -18730,19 +18867,19 @@
         <v>78</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C79" s="17" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="D79" s="17" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E79" s="17" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F79" s="17" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="7"/>
@@ -18772,19 +18909,19 @@
         <v>79</v>
       </c>
       <c r="B80" s="17" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C80" s="17" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="D80" s="17" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E80" s="17" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F80" s="17" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
@@ -18814,19 +18951,19 @@
         <v>80</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C81" s="17" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D81" s="17" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E81" s="17" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F81" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G81" s="7"/>
       <c r="H81" s="7" t="n">
@@ -18878,19 +19015,19 @@
         <v>81</v>
       </c>
       <c r="B82" s="17" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C82" s="17" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D82" s="17" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E82" s="17" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F82" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G82" s="7" t="n">
         <v>0.02</v>
@@ -18954,19 +19091,19 @@
         <v>82</v>
       </c>
       <c r="B83" s="17" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C83" s="17" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D83" s="17" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E83" s="17" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="F83" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G83" s="7" t="n">
         <v>0.01</v>
@@ -19014,19 +19151,19 @@
         <v>83</v>
       </c>
       <c r="B84" s="17" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C84" s="17" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D84" s="17" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E84" s="17" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F84" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G84" s="7" t="n">
         <v>0.01</v>
@@ -19064,19 +19201,19 @@
         <v>84</v>
       </c>
       <c r="B85" s="17" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C85" s="17" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E85" s="17" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F85" s="17" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G85" s="7"/>
       <c r="H85" s="7"/>
@@ -19108,19 +19245,19 @@
         <v>85</v>
       </c>
       <c r="B86" s="17" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C86" s="17" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D86" s="17" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E86" s="17" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="F86" s="17" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G86" s="7" t="n">
         <v>0.15</v>
@@ -19168,19 +19305,19 @@
         <v>86</v>
       </c>
       <c r="B87" s="17" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C87" s="17" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D87" s="17" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E87" s="15" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="F87" s="17" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G87" s="7"/>
       <c r="H87" s="7"/>
@@ -19226,16 +19363,16 @@
         <v>87</v>
       </c>
       <c r="B88" s="17" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C88" s="17" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D88" s="17" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="E88" s="17" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="F88" s="15"/>
       <c r="G88" s="7" t="n">
@@ -19290,19 +19427,19 @@
         <v>88</v>
       </c>
       <c r="B89" s="17" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C89" s="17" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D89" s="17" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="E89" s="17" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F89" s="17" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G89" s="7" t="n">
         <v>0.05</v>
@@ -19336,19 +19473,19 @@
         <v>89</v>
       </c>
       <c r="B90" s="17" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C90" s="17" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D90" s="17" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E90" s="17" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F90" s="17" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G90" s="7" t="n">
         <v>0.05</v>
@@ -19382,19 +19519,19 @@
         <v>90</v>
       </c>
       <c r="B91" s="17" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C91" s="17" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D91" s="15" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E91" s="17" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F91" s="17" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G91" s="7" t="n">
         <v>0.05</v>
@@ -19428,19 +19565,19 @@
         <v>91</v>
       </c>
       <c r="B92" s="17" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C92" s="17" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D92" s="17" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E92" s="17" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F92" s="17" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G92" s="7"/>
       <c r="H92" s="7"/>
@@ -19472,19 +19609,19 @@
         <v>92</v>
       </c>
       <c r="B93" s="17" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C93" s="17" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D93" s="17" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E93" s="17" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="F93" s="17" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G93" s="7" t="n">
         <v>0.02</v>
@@ -19518,19 +19655,19 @@
         <v>93</v>
       </c>
       <c r="B94" s="17" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C94" s="17" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D94" s="17" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E94" s="17" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F94" s="17" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G94" s="7"/>
       <c r="H94" s="7" t="n">
@@ -19562,19 +19699,19 @@
         <v>94</v>
       </c>
       <c r="B95" s="17" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C95" s="17" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D95" s="17" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E95" s="17" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F95" s="17" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G95" s="7"/>
       <c r="H95" s="7" t="n">
@@ -19606,19 +19743,19 @@
         <v>95</v>
       </c>
       <c r="B96" s="17" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C96" s="17" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D96" s="17" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E96" s="17" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F96" s="17" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G96" s="7"/>
       <c r="H96" s="7" t="n">
@@ -19650,19 +19787,19 @@
         <v>96</v>
       </c>
       <c r="B97" s="17" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C97" s="17" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D97" s="17" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E97" s="17" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="F97" s="17" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G97" s="7"/>
       <c r="H97" s="7" t="n">
@@ -19694,19 +19831,19 @@
         <v>97</v>
       </c>
       <c r="B98" s="17" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C98" s="17" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D98" s="17" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E98" s="17" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F98" s="17" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G98" s="7"/>
       <c r="H98" s="7"/>
@@ -19750,19 +19887,19 @@
         <v>98</v>
       </c>
       <c r="B99" s="17" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C99" s="17" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D99" s="15" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E99" s="17" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F99" s="17" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G99" s="7"/>
       <c r="H99" s="7" t="n">
@@ -19808,19 +19945,19 @@
         <v>99</v>
       </c>
       <c r="B100" s="17" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C100" s="17" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D100" s="17" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E100" s="17" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F100" s="17" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G100" s="7"/>
       <c r="H100" s="7"/>
@@ -19854,19 +19991,19 @@
         <v>100</v>
       </c>
       <c r="B101" s="17" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C101" s="17" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D101" s="17" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E101" s="17" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="F101" s="17" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G101" s="7" t="n">
         <v>0.01</v>
@@ -19912,19 +20049,19 @@
         <v>101</v>
       </c>
       <c r="B102" s="17" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C102" s="17" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D102" s="17" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E102" s="17" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F102" s="17" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G102" s="7" t="n">
         <v>0.01</v>
@@ -19958,19 +20095,19 @@
         <v>102</v>
       </c>
       <c r="B103" s="17" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C103" s="17" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D103" s="15" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E103" s="15" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F103" s="17" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G103" s="7" t="n">
         <v>0.01</v>
@@ -20001,7 +20138,7 @@
     </row>
     <row r="104" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D104" s="4" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G104" s="18" t="n">
         <f aca="false">SUM(G2:G103)</f>
@@ -20078,7 +20215,7 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="12" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
   </sheetData>

--- a/docs/tai-ve/Phan-tich-khoi-luong-MD-APIC.xlsx
+++ b/docs/tai-ve/Phan-tich-khoi-luong-MD-APIC.xlsx
@@ -79,7 +79,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">bàn giao cho Khanh (đề xuất 11/2026, muộn nhất 12/2026); điều phối xuất hàng chung cả nhóm; quản lý chung may mẫu</t>
+      <t xml:space="preserve">bàn giao cho Khanh từ 11/2026; điều phối xuất hàng chung cả nhóm; quản lý chung may mẫu</t>
     </r>
   </si>
   <si>
@@ -153,7 +153,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(nhận từ Cuong); hỗ trợ TNF </t>
+      <t xml:space="preserve">(nhận từ Cuong từ 11/2026); hỗ trợ TNF </t>
     </r>
     <r>
       <rPr>
@@ -482,7 +482,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">A. Chỉ các việc đã quyết (NW → Khanh ngay; TNF </t>
+      <t xml:space="preserve">A. Phương án cũ: NW → Khanh ngay; TNF </t>
     </r>
     <r>
       <rPr>
@@ -499,7 +499,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">và 1/3 mẫu TNF → Khanh từ 12/2026)</t>
+      <t xml:space="preserve">và 1/3 mẫu TNF → Khanh từ 12/2026</t>
     </r>
   </si>
   <si>
@@ -525,7 +525,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">C. B + chuyển TNF </t>
+      <t xml:space="preserve">C. B + TNF </t>
     </r>
     <r>
       <rPr>
@@ -533,7 +533,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">東京企画 </t>
+      <t xml:space="preserve">東京企画 → </t>
     </r>
     <r>
       <rPr>
@@ -542,7 +542,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">cho Khanh ngay từ 11/2026</t>
+      <t xml:space="preserve">Khanh từ 11/2026 (đã quyết 28/10/2026)</t>
     </r>
   </si>
   <si>
@@ -4682,7 +4682,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="36.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>14</v>
       </c>

--- a/docs/tai-ve/Phan-tich-khoi-luong-MD-APIC.xlsx
+++ b/docs/tai-ve/Phan-tich-khoi-luong-MD-APIC.xlsx
@@ -32,12 +32,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2404" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2404" uniqueCount="559">
   <si>
     <t xml:space="preserve">Phân công dự kiến nhóm MD APIC (quyết định 10/2026, cập nhật theo Plantable 26/10/2026)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cột 2: 11–12/2026 (mẫu triển lãm 27FW, PPS 27SS, đại trà 27SS bắt đầu). Cột 3: từ mẫu 1st 28SS (1–2/2027). Cột 4: hỗ trợ tạm theo tháng (đề xuất).</t>
+    <t xml:space="preserve">Cột 2: 11–12/2026 (mẫu triển lãm 27FW, PPS 27SS, đại trà 27SS bắt đầu). Cột 3: từ mẫu 1st 28SS (1–2/2027). Hỗ trợ tạm theo tháng: chưa áp dụng.</t>
   </si>
   <si>
     <t xml:space="preserve">Người</t>
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Từ mẫu 1st 28SS (1–2/2027)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ghi chú / hỗ trợ tạm theo tháng</t>
+    <t xml:space="preserve">Ghi chú</t>
   </si>
   <si>
     <t xml:space="preserve">Cuong</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">HELLY HANSEN; điều phối xuất hàng chung; quản lý chung may mẫu</t>
   </si>
   <si>
-    <t xml:space="preserve">Cao điểm 12/2026 (21 mã HH vào chuyền): Huy hỗ trợ ~25%, Nhu ~15%</t>
+    <t xml:space="preserve">Cao điểm 12/2026 (21 mã HH vào chuyền). Hỗ trợ tạm: chưa cần, theo dõi</t>
   </si>
   <si>
     <t xml:space="preserve">Luan</t>
@@ -256,7 +256,7 @@
     <t xml:space="preserve">Như trên, chia 1/3 mẫu TNF cho Khanh</t>
   </si>
   <si>
-    <t xml:space="preserve">1/2027: hỗ trợ Huy ~20%</t>
+    <t xml:space="preserve">Gánh đợt mẫu triển lãm 27FW lớn nhất nhóm (611 cái, gồm YONEX 244)</t>
   </si>
   <si>
     <t xml:space="preserve">Huy</t>
@@ -300,7 +300,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">12/2026 rảnh: hỗ trợ Cuong ~25%. Cao điểm 1/2027 (25 mã </t>
+      <t xml:space="preserve">Cao điểm 1/2027 (25 mã </t>
     </r>
     <r>
       <rPr>
@@ -317,17 +317,17 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">vào chuyền): B.Trang hỗ trợ ~20%</t>
+      <t xml:space="preserve">vào chuyền). Hỗ trợ tạm: chưa cần, theo dõi</t>
     </r>
   </si>
   <si>
     <t xml:space="preserve">Hien</t>
   </si>
   <si>
-    <t xml:space="preserve">Teton Bros, ALLTERRAIN, Mont-Bell, DESCENTE GOLF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Không giao thêm</t>
+    <t xml:space="preserve">Teton Bros, ALLTERRAIN, Mont-Bell, DESCENTE GOLF, Snowpeak (4 lô trên Plantable)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Không giao thêm. Tháng 11–12 khá cao (mẫu SKI, 14 mã vào chuyền tháng 12)</t>
   </si>
   <si>
     <t xml:space="preserve">Nhu</t>
@@ -361,7 +361,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Theo dõi thêm. 12/2026 rảnh: hỗ trợ Cuong ~15%</t>
+    <t xml:space="preserve">Theo dõi thêm</t>
   </si>
   <si>
     <t xml:space="preserve">Chỉ số tải nhóm MD – kỳ vừa qua (bulk 26FW + 27SS, mẫu 27SS)</t>
@@ -1844,9 +1844,6 @@
   </si>
   <si>
     <t xml:space="preserve">Ngày chuyền / ngày may</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ghi chú</t>
   </si>
   <si>
     <t xml:space="preserve">Thuan</t>
@@ -4710,7 +4707,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="36.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
         <v>22</v>
       </c>
@@ -4724,7 +4721,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
         <v>26</v>
       </c>
@@ -5489,7 +5486,7 @@
         <v>1.88</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="E5" s="10" t="n">
         <v>0.15</v>
@@ -5498,10 +5495,10 @@
         <v>1.41</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>1.04</v>
@@ -5515,10 +5512,10 @@
         <v>71</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="E6" s="10" t="n">
         <v>0.75</v>
@@ -5530,7 +5527,7 @@
         <v>0.44</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>0.35</v>
@@ -5544,10 +5541,10 @@
         <v>72</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="E7" s="10" t="n">
         <v>0.11</v>
@@ -5556,13 +5553,13 @@
         <v>0.15</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5573,25 +5570,25 @@
         <v>73</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>0.7</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="F8" s="10" t="n">
         <v>0.11</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="H8" s="10" t="n">
         <v>0.68</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5605,7 +5602,7 @@
         <v>1.88</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="E9" s="10" t="n">
         <v>0.58</v>
@@ -5614,10 +5611,10 @@
         <v>1.41</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>1.04</v>
@@ -5631,13 +5628,13 @@
         <v>71</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="F10" s="10" t="n">
         <v>0.88</v>
@@ -5646,7 +5643,7 @@
         <v>0.44</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>0.35</v>
@@ -5660,10 +5657,10 @@
         <v>72</v>
       </c>
       <c r="C11" s="10" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="E11" s="10" t="n">
         <v>0.8</v>
@@ -5672,13 +5669,13 @@
         <v>0.15</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5689,10 +5686,10 @@
         <v>73</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="E12" s="10" t="n">
         <v>0.64</v>
@@ -5701,13 +5698,13 @@
         <v>0.11</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="H12" s="10" t="n">
         <v>0.68</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5718,22 +5715,22 @@
         <v>70</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="F13" s="13" t="n">
         <v>1.41</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>1.04</v>
@@ -5747,13 +5744,13 @@
         <v>71</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="F14" s="10" t="n">
         <v>0.88</v>
@@ -5762,7 +5759,7 @@
         <v>0.44</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>0.35</v>
@@ -5776,10 +5773,10 @@
         <v>72</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="E15" s="10" t="n">
         <v>0.8</v>
@@ -5788,13 +5785,13 @@
         <v>0.15</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5805,10 +5802,10 @@
         <v>73</v>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>0.64</v>
@@ -5817,13 +5814,13 @@
         <v>0.11</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="H16" s="10" t="n">
         <v>0.68</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5834,22 +5831,22 @@
         <v>70</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="F17" s="13" t="n">
         <v>1.41</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="I17" s="10" t="n">
         <v>1.04</v>
@@ -5863,13 +5860,13 @@
         <v>71</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="F18" s="10" t="n">
         <v>0.88</v>
@@ -5878,7 +5875,7 @@
         <v>0.93</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>0.35</v>
@@ -5892,10 +5889,10 @@
         <v>72</v>
       </c>
       <c r="C19" s="10" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>0.8</v>
@@ -5904,13 +5901,13 @@
         <v>0.47</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5921,10 +5918,10 @@
         <v>73</v>
       </c>
       <c r="C20" s="10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>0.64</v>
@@ -5933,13 +5930,13 @@
         <v>0.11</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="H20" s="10" t="n">
         <v>0.68</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5950,22 +5947,22 @@
         <v>70</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="F21" s="13" t="n">
         <v>1.41</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H21" s="13" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>1.04</v>
@@ -5979,13 +5976,13 @@
         <v>71</v>
       </c>
       <c r="C22" s="10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="F22" s="10" t="n">
         <v>0.88</v>
@@ -5994,10 +5991,10 @@
         <v>0.93</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>0.57</v>
+        <v>0.56</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6008,10 +6005,10 @@
         <v>72</v>
       </c>
       <c r="C23" s="10" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="E23" s="10" t="n">
         <v>0.8</v>
@@ -6020,13 +6017,13 @@
         <v>0.47</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6037,10 +6034,10 @@
         <v>73</v>
       </c>
       <c r="C24" s="10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>0.64</v>
@@ -6049,13 +6046,13 @@
         <v>0.11</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="H24" s="10" t="n">
         <v>0.68</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6115,7 +6112,7 @@
         <v>8</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I28" s="8" t="n">
         <v>3</v>
@@ -6144,7 +6141,7 @@
         <v>1</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I29" s="8" t="n">
         <v>2</v>
@@ -6231,7 +6228,7 @@
         <v>10</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I32" s="8" t="n">
         <v>8</v>
@@ -6260,7 +6257,7 @@
         <v>5</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I33" s="8" t="n">
         <v>3</v>
@@ -6289,7 +6286,7 @@
         <v>26</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I34" s="8" t="n">
         <v>14</v>
@@ -6463,7 +6460,7 @@
         <v>93</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I40" s="8" t="n">
         <v>92</v>
@@ -6492,7 +6489,7 @@
         <v>18</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="I41" s="8" t="n">
         <v>20</v>
@@ -8276,18 +8273,18 @@
         <v>216</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>217</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="B2" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="C2" s="16" t="s">
         <v>219</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>220</v>
       </c>
       <c r="D2" s="17" t="n">
         <v>1581</v>
@@ -8305,13 +8302,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="B3" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="B3" s="16" t="s">
-        <v>219</v>
-      </c>
       <c r="C3" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D3" s="17" t="n">
         <v>345</v>
@@ -8329,13 +8326,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D4" s="17" t="n">
         <v>400</v>
@@ -8353,13 +8350,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D5" s="17" t="n">
         <v>3679</v>
@@ -8377,13 +8374,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D6" s="17" t="n">
         <v>250</v>
@@ -8401,13 +8398,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B7" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="C7" s="16" t="s">
         <v>224</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>225</v>
       </c>
       <c r="D7" s="17" t="n">
         <v>2888</v>
@@ -8425,13 +8422,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D8" s="17" t="n">
         <v>3831</v>
@@ -8449,10 +8446,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>133</v>
@@ -8473,13 +8470,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B10" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="C10" s="16" t="s">
         <v>226</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>227</v>
       </c>
       <c r="D10" s="17" t="n">
         <v>2596</v>
@@ -8497,13 +8494,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D11" s="17" t="n">
         <v>34077</v>
@@ -8521,13 +8518,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D12" s="17" t="n">
         <v>1469</v>
@@ -8545,13 +8542,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D13" s="17" t="n">
         <v>2888</v>
@@ -8569,13 +8566,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D14" s="17" t="n">
         <v>666</v>
@@ -8593,13 +8590,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="C15" s="16" t="s">
         <v>230</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>231</v>
       </c>
       <c r="D15" s="17" t="n">
         <v>278</v>
@@ -8617,13 +8614,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D16" s="17" t="n">
         <v>20226</v>
@@ -8641,13 +8638,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D17" s="17" t="n">
         <v>914</v>
@@ -8665,13 +8662,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D18" s="17" t="n">
         <v>548</v>
@@ -8689,13 +8686,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D19" s="17" t="n">
         <v>3782</v>
@@ -8713,13 +8710,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D20" s="17" t="n">
         <v>5400</v>
@@ -8737,13 +8734,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D21" s="17" t="n">
         <v>16154</v>
@@ -8761,13 +8758,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="C22" s="16" t="s">
         <v>230</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>231</v>
       </c>
       <c r="D22" s="17" t="n">
         <v>1050</v>
@@ -8785,13 +8782,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D23" s="17" t="n">
         <v>18185</v>
@@ -8809,13 +8806,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="C24" s="16" t="s">
         <v>230</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>231</v>
       </c>
       <c r="D24" s="17" t="n">
         <v>250</v>
@@ -8833,13 +8830,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D25" s="17" t="n">
         <v>12276</v>
@@ -8857,13 +8854,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="C26" s="16" t="s">
         <v>230</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>231</v>
       </c>
       <c r="D26" s="17" t="n">
         <v>821</v>
@@ -8881,13 +8878,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D27" s="17" t="n">
         <v>7355</v>
@@ -8908,10 +8905,10 @@
         <v>6</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D28" s="17" t="n">
         <v>9350</v>
@@ -8932,7 +8929,7 @@
         <v>6</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C29" s="16" t="s">
         <v>130</v>
@@ -8956,10 +8953,10 @@
         <v>6</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D30" s="17" t="n">
         <v>1608</v>
@@ -8980,10 +8977,10 @@
         <v>6</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D31" s="17" t="n">
         <v>2000</v>
@@ -9004,10 +9001,10 @@
         <v>6</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D32" s="17" t="n">
         <v>50717</v>
@@ -9028,10 +9025,10 @@
         <v>6</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D33" s="17" t="n">
         <v>21965</v>
@@ -9052,7 +9049,7 @@
         <v>6</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C34" s="16" t="s">
         <v>130</v>
@@ -9076,10 +9073,10 @@
         <v>6</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D35" s="17" t="n">
         <v>5815</v>
@@ -9100,10 +9097,10 @@
         <v>6</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D36" s="17" t="n">
         <v>2000</v>
@@ -9124,10 +9121,10 @@
         <v>6</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D37" s="17" t="n">
         <v>10763</v>
@@ -9148,10 +9145,10 @@
         <v>6</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D38" s="17" t="n">
         <v>9108</v>
@@ -9172,10 +9169,10 @@
         <v>6</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D39" s="17" t="n">
         <v>9120</v>
@@ -9196,7 +9193,7 @@
         <v>6</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C40" s="16" t="s">
         <v>130</v>
@@ -9220,10 +9217,10 @@
         <v>6</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D41" s="17" t="n">
         <v>30496</v>
@@ -9244,7 +9241,7 @@
         <v>6</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C42" s="16" t="s">
         <v>130</v>
@@ -9268,10 +9265,10 @@
         <v>6</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D43" s="17" t="n">
         <v>1701</v>
@@ -9292,10 +9289,10 @@
         <v>6</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D44" s="17" t="n">
         <v>16804</v>
@@ -9316,10 +9313,10 @@
         <v>6</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D45" s="17" t="n">
         <v>12067</v>
@@ -9340,10 +9337,10 @@
         <v>6</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D46" s="17" t="n">
         <v>329</v>
@@ -9364,7 +9361,7 @@
         <v>6</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C47" s="16" t="s">
         <v>130</v>
@@ -9388,10 +9385,10 @@
         <v>6</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D48" s="17" t="n">
         <v>6003</v>
@@ -9412,10 +9409,10 @@
         <v>6</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D49" s="17" t="n">
         <v>150</v>
@@ -9436,10 +9433,10 @@
         <v>6</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D50" s="17" t="n">
         <v>21124</v>
@@ -9460,10 +9457,10 @@
         <v>6</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D51" s="17" t="n">
         <v>5199</v>
@@ -9484,7 +9481,7 @@
         <v>6</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C52" s="16" t="s">
         <v>130</v>
@@ -9508,10 +9505,10 @@
         <v>6</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D53" s="17" t="n">
         <v>15800</v>
@@ -9532,10 +9529,10 @@
         <v>6</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D54" s="17" t="n">
         <v>7795</v>
@@ -9556,7 +9553,7 @@
         <v>6</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C55" s="16" t="s">
         <v>130</v>
@@ -9580,10 +9577,10 @@
         <v>6</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D56" s="17" t="n">
         <v>4882</v>
@@ -9604,10 +9601,10 @@
         <v>6</v>
       </c>
       <c r="B57" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="C57" s="16" t="s">
         <v>243</v>
-      </c>
-      <c r="C57" s="16" t="s">
-        <v>244</v>
       </c>
       <c r="D57" s="17" t="n">
         <v>6131</v>
@@ -9628,10 +9625,10 @@
         <v>6</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D58" s="17" t="n">
         <v>805</v>
@@ -9652,10 +9649,10 @@
         <v>6</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D59" s="17" t="n">
         <v>109487</v>
@@ -9676,7 +9673,7 @@
         <v>6</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C60" s="16" t="s">
         <v>130</v>
@@ -9700,10 +9697,10 @@
         <v>6</v>
       </c>
       <c r="B61" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="C61" s="16" t="s">
         <v>246</v>
-      </c>
-      <c r="C61" s="16" t="s">
-        <v>247</v>
       </c>
       <c r="D61" s="17" t="n">
         <v>874</v>
@@ -9724,10 +9721,10 @@
         <v>6</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D62" s="17" t="n">
         <v>19320</v>
@@ -9748,7 +9745,7 @@
         <v>6</v>
       </c>
       <c r="B63" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C63" s="16" t="s">
         <v>133</v>
@@ -9772,7 +9769,7 @@
         <v>6</v>
       </c>
       <c r="B64" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C64" s="16" t="s">
         <v>130</v>
@@ -9796,10 +9793,10 @@
         <v>6</v>
       </c>
       <c r="B65" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C65" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D65" s="17" t="n">
         <v>35392</v>
@@ -9820,7 +9817,7 @@
         <v>6</v>
       </c>
       <c r="B66" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C66" s="16" t="s">
         <v>133</v>
@@ -9844,7 +9841,7 @@
         <v>6</v>
       </c>
       <c r="B67" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C67" s="16" t="s">
         <v>130</v>
@@ -9868,10 +9865,10 @@
         <v>6</v>
       </c>
       <c r="B68" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C68" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D68" s="17" t="n">
         <v>14612</v>
@@ -9892,7 +9889,7 @@
         <v>6</v>
       </c>
       <c r="B69" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C69" s="16" t="s">
         <v>133</v>
@@ -9916,7 +9913,7 @@
         <v>6</v>
       </c>
       <c r="B70" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C70" s="16" t="s">
         <v>130</v>
@@ -9940,10 +9937,10 @@
         <v>6</v>
       </c>
       <c r="B71" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="C71" s="16" t="s">
         <v>250</v>
-      </c>
-      <c r="C71" s="16" t="s">
-        <v>251</v>
       </c>
       <c r="D71" s="17" t="n">
         <v>518</v>
@@ -9964,10 +9961,10 @@
         <v>6</v>
       </c>
       <c r="B72" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C72" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D72" s="17" t="n">
         <v>41883</v>
@@ -9988,7 +9985,7 @@
         <v>6</v>
       </c>
       <c r="B73" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C73" s="16" t="s">
         <v>133</v>
@@ -10012,7 +10009,7 @@
         <v>6</v>
       </c>
       <c r="B74" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C74" s="16" t="s">
         <v>130</v>
@@ -10036,7 +10033,7 @@
         <v>6</v>
       </c>
       <c r="B75" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C75" s="16" t="s">
         <v>133</v>
@@ -10060,7 +10057,7 @@
         <v>6</v>
       </c>
       <c r="B76" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C76" s="16" t="s">
         <v>130</v>
@@ -10078,7 +10075,7 @@
         <v>529</v>
       </c>
       <c r="H76" s="18" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10086,10 +10083,10 @@
         <v>6</v>
       </c>
       <c r="B77" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C77" s="16" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D77" s="17" t="n">
         <v>3465</v>
@@ -10110,10 +10107,10 @@
         <v>6</v>
       </c>
       <c r="B78" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C78" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D78" s="17" t="n">
         <v>18885</v>
@@ -10134,7 +10131,7 @@
         <v>6</v>
       </c>
       <c r="B79" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C79" s="16" t="s">
         <v>133</v>
@@ -10158,7 +10155,7 @@
         <v>6</v>
       </c>
       <c r="B80" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C80" s="16" t="s">
         <v>130</v>
@@ -10182,10 +10179,10 @@
         <v>26</v>
       </c>
       <c r="B81" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C81" s="16" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D81" s="17" t="n">
         <v>1476</v>
@@ -10206,10 +10203,10 @@
         <v>26</v>
       </c>
       <c r="B82" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C82" s="16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D82" s="17" t="n">
         <v>15886</v>
@@ -10230,10 +10227,10 @@
         <v>26</v>
       </c>
       <c r="B83" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C83" s="16" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D83" s="17" t="n">
         <v>3911</v>
@@ -10254,10 +10251,10 @@
         <v>26</v>
       </c>
       <c r="B84" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C84" s="16" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D84" s="17" t="n">
         <v>2632</v>
@@ -10278,10 +10275,10 @@
         <v>26</v>
       </c>
       <c r="B85" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C85" s="16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D85" s="17" t="n">
         <v>9594</v>
@@ -10302,10 +10299,10 @@
         <v>26</v>
       </c>
       <c r="B86" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C86" s="16" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D86" s="17" t="n">
         <v>1382</v>
@@ -10326,10 +10323,10 @@
         <v>26</v>
       </c>
       <c r="B87" s="16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C87" s="16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D87" s="17" t="n">
         <v>4988</v>
@@ -10350,10 +10347,10 @@
         <v>26</v>
       </c>
       <c r="B88" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C88" s="16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D88" s="17" t="n">
         <v>5931</v>
@@ -10374,10 +10371,10 @@
         <v>26</v>
       </c>
       <c r="B89" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C89" s="16" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D89" s="17" t="n">
         <v>1630</v>
@@ -10398,10 +10395,10 @@
         <v>26</v>
       </c>
       <c r="B90" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C90" s="16" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D90" s="17" t="n">
         <v>3380</v>
@@ -10422,10 +10419,10 @@
         <v>26</v>
       </c>
       <c r="B91" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C91" s="16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D91" s="17" t="n">
         <v>1610</v>
@@ -10446,10 +10443,10 @@
         <v>26</v>
       </c>
       <c r="B92" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C92" s="16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D92" s="17" t="n">
         <v>5931</v>
@@ -10470,10 +10467,10 @@
         <v>26</v>
       </c>
       <c r="B93" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C93" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D93" s="17" t="n">
         <v>772</v>
@@ -10494,10 +10491,10 @@
         <v>26</v>
       </c>
       <c r="B94" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C94" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D94" s="17" t="n">
         <v>16784</v>
@@ -10518,10 +10515,10 @@
         <v>26</v>
       </c>
       <c r="B95" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C95" s="16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D95" s="17" t="n">
         <v>1484</v>
@@ -10542,10 +10539,10 @@
         <v>26</v>
       </c>
       <c r="B96" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C96" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D96" s="17" t="n">
         <v>301</v>
@@ -10566,10 +10563,10 @@
         <v>26</v>
       </c>
       <c r="B97" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C97" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D97" s="17" t="n">
         <v>7592</v>
@@ -10590,10 +10587,10 @@
         <v>26</v>
       </c>
       <c r="B98" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C98" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D98" s="17" t="n">
         <v>998</v>
@@ -10614,10 +10611,10 @@
         <v>26</v>
       </c>
       <c r="B99" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C99" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D99" s="17" t="n">
         <v>4455</v>
@@ -10638,10 +10635,10 @@
         <v>26</v>
       </c>
       <c r="B100" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C100" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D100" s="17" t="n">
         <v>13869</v>
@@ -10662,10 +10659,10 @@
         <v>26</v>
       </c>
       <c r="B101" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C101" s="16" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D101" s="17" t="n">
         <v>10000</v>
@@ -10686,10 +10683,10 @@
         <v>26</v>
       </c>
       <c r="B102" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C102" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D102" s="17" t="n">
         <v>20608</v>
@@ -10710,10 +10707,10 @@
         <v>26</v>
       </c>
       <c r="B103" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C103" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D103" s="17" t="n">
         <v>7683</v>
@@ -10734,10 +10731,10 @@
         <v>26</v>
       </c>
       <c r="B104" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C104" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D104" s="17" t="n">
         <v>5065</v>
@@ -10758,10 +10755,10 @@
         <v>26</v>
       </c>
       <c r="B105" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C105" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D105" s="17" t="n">
         <v>10117</v>
@@ -10782,10 +10779,10 @@
         <v>26</v>
       </c>
       <c r="B106" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C106" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D106" s="17" t="n">
         <v>966</v>
@@ -10806,10 +10803,10 @@
         <v>26</v>
       </c>
       <c r="B107" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C107" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D107" s="17" t="n">
         <v>25802</v>
@@ -10830,10 +10827,10 @@
         <v>26</v>
       </c>
       <c r="B108" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C108" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D108" s="17" t="n">
         <v>655</v>
@@ -10854,10 +10851,10 @@
         <v>26</v>
       </c>
       <c r="B109" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C109" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D109" s="17" t="n">
         <v>829</v>
@@ -10878,10 +10875,10 @@
         <v>26</v>
       </c>
       <c r="B110" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C110" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D110" s="17" t="n">
         <v>46521</v>
@@ -10902,10 +10899,10 @@
         <v>26</v>
       </c>
       <c r="B111" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C111" s="16" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D111" s="17" t="n">
         <v>3644</v>
@@ -10926,10 +10923,10 @@
         <v>26</v>
       </c>
       <c r="B112" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C112" s="16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D112" s="17" t="n">
         <v>611</v>
@@ -10950,10 +10947,10 @@
         <v>26</v>
       </c>
       <c r="B113" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C113" s="16" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D113" s="17" t="n">
         <v>9748</v>
@@ -10974,10 +10971,10 @@
         <v>26</v>
       </c>
       <c r="B114" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C114" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D114" s="17" t="n">
         <v>3044</v>
@@ -10998,10 +10995,10 @@
         <v>26</v>
       </c>
       <c r="B115" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C115" s="16" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D115" s="17" t="n">
         <v>2721</v>
@@ -11022,10 +11019,10 @@
         <v>26</v>
       </c>
       <c r="B116" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C116" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D116" s="17" t="n">
         <v>24594</v>
@@ -11046,10 +11043,10 @@
         <v>26</v>
       </c>
       <c r="B117" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C117" s="16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D117" s="17" t="n">
         <v>3000</v>
@@ -11070,10 +11067,10 @@
         <v>26</v>
       </c>
       <c r="B118" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C118" s="16" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D118" s="17" t="n">
         <v>2912</v>
@@ -11094,10 +11091,10 @@
         <v>26</v>
       </c>
       <c r="B119" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C119" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D119" s="17" t="n">
         <v>13195</v>
@@ -11118,10 +11115,10 @@
         <v>26</v>
       </c>
       <c r="B120" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C120" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D120" s="17" t="n">
         <v>15287</v>
@@ -11142,10 +11139,10 @@
         <v>26</v>
       </c>
       <c r="B121" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C121" s="16" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D121" s="17" t="n">
         <v>6781</v>
@@ -11166,10 +11163,10 @@
         <v>26</v>
       </c>
       <c r="B122" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C122" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D122" s="17" t="n">
         <v>12594</v>
@@ -11190,10 +11187,10 @@
         <v>26</v>
       </c>
       <c r="B123" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C123" s="16" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D123" s="17" t="n">
         <v>900</v>
@@ -11214,10 +11211,10 @@
         <v>29</v>
       </c>
       <c r="B124" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C124" s="16" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D124" s="17" t="n">
         <v>1060</v>
@@ -11238,10 +11235,10 @@
         <v>29</v>
       </c>
       <c r="B125" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C125" s="16" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D125" s="17" t="n">
         <v>700</v>
@@ -11262,10 +11259,10 @@
         <v>29</v>
       </c>
       <c r="B126" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C126" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D126" s="17" t="n">
         <v>19607</v>
@@ -11286,10 +11283,10 @@
         <v>29</v>
       </c>
       <c r="B127" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C127" s="16" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D127" s="17" t="n">
         <v>10440</v>
@@ -11310,10 +11307,10 @@
         <v>29</v>
       </c>
       <c r="B128" s="16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C128" s="16" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D128" s="17" t="n">
         <v>4418</v>
@@ -11334,10 +11331,10 @@
         <v>29</v>
       </c>
       <c r="B129" s="16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C129" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D129" s="17" t="n">
         <v>13632</v>
@@ -11358,10 +11355,10 @@
         <v>29</v>
       </c>
       <c r="B130" s="16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C130" s="16" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D130" s="17" t="n">
         <v>443</v>
@@ -11382,10 +11379,10 @@
         <v>29</v>
       </c>
       <c r="B131" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C131" s="16" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D131" s="17" t="n">
         <v>890</v>
@@ -11406,10 +11403,10 @@
         <v>29</v>
       </c>
       <c r="B132" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C132" s="16" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D132" s="17" t="n">
         <v>9500</v>
@@ -11430,10 +11427,10 @@
         <v>29</v>
       </c>
       <c r="B133" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C133" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D133" s="17" t="n">
         <v>12090</v>
@@ -11454,10 +11451,10 @@
         <v>29</v>
       </c>
       <c r="B134" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C134" s="16" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D134" s="17" t="n">
         <v>10000</v>
@@ -11478,10 +11475,10 @@
         <v>29</v>
       </c>
       <c r="B135" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C135" s="16" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D135" s="17" t="n">
         <v>3070</v>
@@ -11502,10 +11499,10 @@
         <v>29</v>
       </c>
       <c r="B136" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C136" s="16" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D136" s="17" t="n">
         <v>2120</v>
@@ -11526,10 +11523,10 @@
         <v>29</v>
       </c>
       <c r="B137" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C137" s="16" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D137" s="17" t="n">
         <v>1002</v>
@@ -11550,10 +11547,10 @@
         <v>29</v>
       </c>
       <c r="B138" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C138" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D138" s="17" t="n">
         <v>10602</v>
@@ -11574,10 +11571,10 @@
         <v>29</v>
       </c>
       <c r="B139" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C139" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D139" s="17" t="n">
         <v>455</v>
@@ -11598,10 +11595,10 @@
         <v>29</v>
       </c>
       <c r="B140" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C140" s="16" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D140" s="17" t="n">
         <v>890</v>
@@ -11622,10 +11619,10 @@
         <v>29</v>
       </c>
       <c r="B141" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C141" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D141" s="17" t="n">
         <v>12090</v>
@@ -11646,7 +11643,7 @@
         <v>29</v>
       </c>
       <c r="B142" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C142" s="16" t="s">
         <v>133</v>
@@ -11670,10 +11667,10 @@
         <v>29</v>
       </c>
       <c r="B143" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C143" s="16" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D143" s="17" t="n">
         <v>627</v>
@@ -11694,7 +11691,7 @@
         <v>29</v>
       </c>
       <c r="B144" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C144" s="16" t="s">
         <v>133</v>
@@ -11718,10 +11715,10 @@
         <v>29</v>
       </c>
       <c r="B145" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C145" s="16" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D145" s="17" t="n">
         <v>2151</v>
@@ -11742,7 +11739,7 @@
         <v>29</v>
       </c>
       <c r="B146" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C146" s="16" t="s">
         <v>133</v>
@@ -11766,10 +11763,10 @@
         <v>29</v>
       </c>
       <c r="B147" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C147" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D147" s="17" t="n">
         <v>40162</v>
@@ -11790,10 +11787,10 @@
         <v>29</v>
       </c>
       <c r="B148" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C148" s="16" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D148" s="17" t="n">
         <v>812</v>
@@ -11814,7 +11811,7 @@
         <v>29</v>
       </c>
       <c r="B149" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C149" s="16" t="s">
         <v>133</v>
@@ -11838,10 +11835,10 @@
         <v>29</v>
       </c>
       <c r="B150" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C150" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D150" s="17" t="n">
         <v>84339</v>
@@ -11862,10 +11859,10 @@
         <v>29</v>
       </c>
       <c r="B151" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C151" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D151" s="17" t="n">
         <v>26353</v>
@@ -11886,10 +11883,10 @@
         <v>29</v>
       </c>
       <c r="B152" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C152" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D152" s="17" t="n">
         <v>2381</v>
@@ -11908,10 +11905,10 @@
         <v>29</v>
       </c>
       <c r="B153" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C153" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D153" s="17" t="n">
         <v>48965</v>
@@ -11932,10 +11929,10 @@
         <v>29</v>
       </c>
       <c r="B154" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C154" s="16" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D154" s="17" t="n">
         <v>2187</v>
@@ -11956,10 +11953,10 @@
         <v>29</v>
       </c>
       <c r="B155" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C155" s="16" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D155" s="17" t="n">
         <v>35860</v>
@@ -11980,10 +11977,10 @@
         <v>29</v>
       </c>
       <c r="B156" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C156" s="16" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D156" s="17" t="n">
         <v>47395</v>
@@ -12004,10 +12001,10 @@
         <v>29</v>
       </c>
       <c r="B157" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C157" s="16" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D157" s="17" t="n">
         <v>2226</v>
@@ -12028,10 +12025,10 @@
         <v>29</v>
       </c>
       <c r="B158" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C158" s="16" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D158" s="17" t="n">
         <v>56164</v>
@@ -12052,10 +12049,10 @@
         <v>29</v>
       </c>
       <c r="B159" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C159" s="16" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D159" s="17" t="n">
         <v>32056</v>
@@ -12076,10 +12073,10 @@
         <v>10</v>
       </c>
       <c r="B160" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C160" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D160" s="17" t="n">
         <v>88966</v>
@@ -12100,10 +12097,10 @@
         <v>10</v>
       </c>
       <c r="B161" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C161" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D161" s="17" t="n">
         <v>172681</v>
@@ -12124,10 +12121,10 @@
         <v>10</v>
       </c>
       <c r="B162" s="16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C162" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D162" s="17" t="n">
         <v>130371</v>
@@ -12148,10 +12145,10 @@
         <v>10</v>
       </c>
       <c r="B163" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C163" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D163" s="17" t="n">
         <v>370639</v>
@@ -12172,10 +12169,10 @@
         <v>10</v>
       </c>
       <c r="B164" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C164" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D164" s="17" t="n">
         <v>175387</v>
@@ -12196,10 +12193,10 @@
         <v>10</v>
       </c>
       <c r="B165" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C165" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D165" s="17" t="n">
         <v>134787</v>
@@ -12220,10 +12217,10 @@
         <v>10</v>
       </c>
       <c r="B166" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C166" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D166" s="17" t="n">
         <v>189937</v>
@@ -12244,10 +12241,10 @@
         <v>10</v>
       </c>
       <c r="B167" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C167" s="16" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D167" s="17" t="n">
         <v>994</v>
@@ -12268,10 +12265,10 @@
         <v>10</v>
       </c>
       <c r="B168" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C168" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D168" s="17" t="n">
         <v>160051</v>
@@ -12292,10 +12289,10 @@
         <v>10</v>
       </c>
       <c r="B169" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C169" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D169" s="17" t="n">
         <v>13638</v>
@@ -12316,10 +12313,10 @@
         <v>10</v>
       </c>
       <c r="B170" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C170" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D170" s="17" t="n">
         <v>200411</v>
@@ -12340,10 +12337,10 @@
         <v>10</v>
       </c>
       <c r="B171" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C171" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D171" s="17" t="n">
         <v>160572</v>
@@ -12364,10 +12361,10 @@
         <v>10</v>
       </c>
       <c r="B172" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C172" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D172" s="17" t="n">
         <v>200202</v>
@@ -12388,10 +12385,10 @@
         <v>10</v>
       </c>
       <c r="B173" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C173" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D173" s="17" t="n">
         <v>144941</v>
@@ -12412,10 +12409,10 @@
         <v>10</v>
       </c>
       <c r="B174" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C174" s="16" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D174" s="17" t="n">
         <v>28056</v>
@@ -12436,10 +12433,10 @@
         <v>10</v>
       </c>
       <c r="B175" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C175" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D175" s="17" t="n">
         <v>167156</v>
@@ -12460,10 +12457,10 @@
         <v>10</v>
       </c>
       <c r="B176" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C176" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D176" s="17" t="n">
         <v>100919</v>
@@ -12484,10 +12481,10 @@
         <v>10</v>
       </c>
       <c r="B177" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C177" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D177" s="17" t="n">
         <v>179012</v>
@@ -12508,10 +12505,10 @@
         <v>10</v>
       </c>
       <c r="B178" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C178" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D178" s="17" t="n">
         <v>207757</v>
@@ -12532,10 +12529,10 @@
         <v>14</v>
       </c>
       <c r="B179" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C179" s="16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D179" s="17" t="n">
         <v>1350</v>
@@ -12556,10 +12553,10 @@
         <v>14</v>
       </c>
       <c r="B180" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C180" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D180" s="17" t="n">
         <v>1969</v>
@@ -12580,10 +12577,10 @@
         <v>14</v>
       </c>
       <c r="B181" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C181" s="16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D181" s="17" t="n">
         <v>1138</v>
@@ -12604,10 +12601,10 @@
         <v>14</v>
       </c>
       <c r="B182" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C182" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D182" s="17" t="n">
         <v>3963</v>
@@ -12628,10 +12625,10 @@
         <v>14</v>
       </c>
       <c r="B183" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C183" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D183" s="17" t="n">
         <v>6361</v>
@@ -12652,10 +12649,10 @@
         <v>14</v>
       </c>
       <c r="B184" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C184" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D184" s="17" t="n">
         <v>2297</v>
@@ -12676,10 +12673,10 @@
         <v>14</v>
       </c>
       <c r="B185" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C185" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D185" s="17" t="n">
         <v>3824</v>
@@ -12700,10 +12697,10 @@
         <v>14</v>
       </c>
       <c r="B186" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C186" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D186" s="17" t="n">
         <v>3823</v>
@@ -12724,10 +12721,10 @@
         <v>14</v>
       </c>
       <c r="B187" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C187" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D187" s="17" t="n">
         <v>20545</v>
@@ -12748,10 +12745,10 @@
         <v>14</v>
       </c>
       <c r="B188" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C188" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D188" s="17" t="n">
         <v>15631</v>
@@ -12772,10 +12769,10 @@
         <v>14</v>
       </c>
       <c r="B189" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C189" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D189" s="17" t="n">
         <v>18775</v>
@@ -12796,10 +12793,10 @@
         <v>14</v>
       </c>
       <c r="B190" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C190" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D190" s="17" t="n">
         <v>22139</v>
@@ -12817,13 +12814,13 @@
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B191" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C191" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D191" s="17" t="n">
         <v>23182</v>
@@ -12841,13 +12838,13 @@
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B192" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C192" s="16" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D192" s="17" t="n">
         <v>2223</v>
@@ -12865,13 +12862,13 @@
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B193" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C193" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D193" s="17" t="n">
         <v>19732</v>
@@ -12889,13 +12886,13 @@
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="B194" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="C194" s="16" t="s">
         <v>278</v>
-      </c>
-      <c r="B194" s="16" t="s">
-        <v>248</v>
-      </c>
-      <c r="C194" s="16" t="s">
-        <v>279</v>
       </c>
       <c r="D194" s="17" t="n">
         <v>50</v>
@@ -12913,13 +12910,13 @@
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B195" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C195" s="16" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D195" s="17" t="n">
         <v>500</v>
@@ -12937,13 +12934,13 @@
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B196" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C196" s="16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D196" s="17" t="n">
         <v>3892</v>
@@ -12961,13 +12958,13 @@
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B197" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C197" s="16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D197" s="17" t="n">
         <v>3373</v>
@@ -12985,13 +12982,13 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="B198" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="C198" s="16" t="s">
         <v>278</v>
-      </c>
-      <c r="B198" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="C198" s="16" t="s">
-        <v>279</v>
       </c>
       <c r="D198" s="17" t="n">
         <v>3813</v>
@@ -13009,13 +13006,13 @@
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B199" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C199" s="16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D199" s="17" t="n">
         <v>290</v>
@@ -13033,13 +13030,13 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B200" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C200" s="16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D200" s="17" t="n">
         <v>2061</v>
@@ -13057,13 +13054,13 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B201" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C201" s="16" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D201" s="17" t="n">
         <v>6</v>
@@ -13081,13 +13078,13 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="B202" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="C202" s="16" t="s">
         <v>278</v>
-      </c>
-      <c r="B202" s="16" t="s">
-        <v>250</v>
-      </c>
-      <c r="C202" s="16" t="s">
-        <v>279</v>
       </c>
       <c r="D202" s="17" t="n">
         <v>1099</v>
@@ -13105,13 +13102,13 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B203" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C203" s="16" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D203" s="17" t="n">
         <v>300</v>
@@ -13129,13 +13126,13 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B204" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C204" s="16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D204" s="17" t="n">
         <v>1916</v>
@@ -13153,13 +13150,13 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B205" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C205" s="16" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D205" s="17" t="n">
         <v>52</v>
@@ -13177,13 +13174,13 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="B206" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="C206" s="16" t="s">
         <v>278</v>
-      </c>
-      <c r="B206" s="16" t="s">
-        <v>252</v>
-      </c>
-      <c r="C206" s="16" t="s">
-        <v>279</v>
       </c>
       <c r="D206" s="17" t="n">
         <v>9386</v>
@@ -13201,13 +13198,13 @@
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B207" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C207" s="16" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D207" s="17" t="n">
         <v>298</v>
@@ -13225,13 +13222,13 @@
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="B208" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="C208" s="16" t="s">
         <v>278</v>
-      </c>
-      <c r="B208" s="16" t="s">
-        <v>253</v>
-      </c>
-      <c r="C208" s="16" t="s">
-        <v>279</v>
       </c>
       <c r="D208" s="17" t="n">
         <v>20689</v>
@@ -13246,18 +13243,18 @@
         <v>366</v>
       </c>
       <c r="H208" s="16" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B209" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C209" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D209" s="17" t="n">
         <v>27289</v>
@@ -13272,18 +13269,18 @@
         <v>511</v>
       </c>
       <c r="H209" s="16" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B210" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C210" s="16" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D210" s="17" t="n">
         <v>200</v>
@@ -13301,13 +13298,13 @@
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B211" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C211" s="16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D211" s="17" t="n">
         <v>2582</v>
@@ -13325,13 +13322,13 @@
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="B212" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="C212" s="16" t="s">
         <v>278</v>
-      </c>
-      <c r="B212" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="C212" s="16" t="s">
-        <v>279</v>
       </c>
       <c r="D212" s="17" t="n">
         <v>11323</v>
@@ -13349,13 +13346,13 @@
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B213" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C213" s="16" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D213" s="17" t="n">
         <v>811</v>
@@ -13373,13 +13370,13 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B214" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C214" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D214" s="17" t="n">
         <v>14305</v>
@@ -13397,13 +13394,13 @@
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="B215" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="C215" s="16" t="s">
         <v>285</v>
-      </c>
-      <c r="B215" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="C215" s="16" t="s">
-        <v>286</v>
       </c>
       <c r="D215" s="17" t="n">
         <v>2675</v>
@@ -13421,13 +13418,13 @@
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="B216" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="C216" s="16" t="s">
         <v>285</v>
-      </c>
-      <c r="B216" s="16" t="s">
-        <v>250</v>
-      </c>
-      <c r="C216" s="16" t="s">
-        <v>286</v>
       </c>
       <c r="D216" s="17" t="n">
         <v>500</v>
@@ -13445,13 +13442,13 @@
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="B217" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="C217" s="16" t="s">
         <v>285</v>
-      </c>
-      <c r="B217" s="16" t="s">
-        <v>252</v>
-      </c>
-      <c r="C217" s="16" t="s">
-        <v>286</v>
       </c>
       <c r="D217" s="17" t="n">
         <v>384</v>
@@ -13466,18 +13463,18 @@
         <v>768</v>
       </c>
       <c r="H217" s="16" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="B218" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="C218" s="16" t="s">
         <v>288</v>
-      </c>
-      <c r="B218" s="16" t="s">
-        <v>252</v>
-      </c>
-      <c r="C218" s="16" t="s">
-        <v>289</v>
       </c>
       <c r="D218" s="17" t="n">
         <v>10000</v>
@@ -13495,10 +13492,10 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="16" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B219" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C219" s="16" t="s">
         <v>122</v>
@@ -13519,13 +13516,13 @@
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="16" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B220" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C220" s="16" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D220" s="17" t="n">
         <v>1046</v>
@@ -13543,13 +13540,13 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="16" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B221" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C221" s="16" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D221" s="17" t="n">
         <v>311</v>
@@ -13603,7 +13600,7 @@
         <v>92</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>95</v>
@@ -13618,7 +13615,7 @@
         <v>216</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>217</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13626,13 +13623,13 @@
         <v>10</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E2" s="17" t="n">
         <v>18</v>
@@ -13653,13 +13650,13 @@
         <v>10</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E3" s="17" t="n">
         <v>55</v>
@@ -13680,13 +13677,13 @@
         <v>10</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E4" s="17" t="n">
         <v>109</v>
@@ -13707,13 +13704,13 @@
         <v>10</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E5" s="17" t="n">
         <v>16</v>
@@ -13734,13 +13731,13 @@
         <v>10</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>18</v>
@@ -13761,13 +13758,13 @@
         <v>10</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E7" s="17" t="n">
         <v>52</v>
@@ -13786,13 +13783,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E8" s="17" t="n">
         <v>12</v>
@@ -13811,13 +13808,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>133</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E9" s="17" t="n">
         <v>18</v>
@@ -13838,13 +13835,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>15</v>
@@ -13865,13 +13862,13 @@
         <v>6</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E11" s="17" t="n">
         <v>2</v>
@@ -13892,13 +13889,13 @@
         <v>6</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C12" s="16" t="s">
         <v>133</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E12" s="17" t="n">
         <v>54</v>
@@ -13919,13 +13916,13 @@
         <v>6</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E13" s="17" t="n">
         <v>8</v>
@@ -13946,13 +13943,13 @@
         <v>6</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>133</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E14" s="17" t="n">
         <v>18</v>
@@ -13973,13 +13970,13 @@
         <v>6</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E15" s="17" t="n">
         <v>1</v>
@@ -14000,13 +13997,13 @@
         <v>6</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E16" s="17" t="n">
         <v>2</v>
@@ -14025,13 +14022,13 @@
         <v>6</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>130</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E17" s="17" t="n">
         <v>7</v>
@@ -14052,13 +14049,13 @@
         <v>6</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>133</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E18" s="17" t="n">
         <v>71</v>
@@ -14079,13 +14076,13 @@
         <v>6</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C19" s="16" t="s">
         <v>130</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E19" s="17" t="n">
         <v>60</v>
@@ -14106,13 +14103,13 @@
         <v>6</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C20" s="16" t="s">
         <v>133</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E20" s="17" t="n">
         <v>15</v>
@@ -14133,13 +14130,13 @@
         <v>6</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E21" s="17" t="n">
         <v>1</v>
@@ -14158,13 +14155,13 @@
         <v>6</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C22" s="16" t="s">
         <v>130</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E22" s="17" t="n">
         <v>10</v>
@@ -14185,13 +14182,13 @@
         <v>6</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E23" s="17" t="n">
         <v>1</v>
@@ -14212,13 +14209,13 @@
         <v>6</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C24" s="16" t="s">
         <v>133</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E24" s="17" t="n">
         <v>78</v>
@@ -14239,13 +14236,13 @@
         <v>6</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>130</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E25" s="17" t="n">
         <v>54</v>
@@ -14266,13 +14263,13 @@
         <v>6</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E26" s="17" t="n">
         <v>6</v>
@@ -14293,13 +14290,13 @@
         <v>6</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>133</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E27" s="17" t="n">
         <v>25</v>
@@ -14320,13 +14317,13 @@
         <v>6</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>130</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E28" s="17" t="n">
         <v>31</v>
@@ -14347,13 +14344,13 @@
         <v>6</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C29" s="16" t="s">
         <v>133</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E29" s="17" t="n">
         <v>63</v>
@@ -14374,13 +14371,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>130</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E30" s="17" t="n">
         <v>56</v>
@@ -14401,13 +14398,13 @@
         <v>6</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E31" s="17" t="n">
         <v>5</v>
@@ -14428,13 +14425,13 @@
         <v>6</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C32" s="16" t="s">
         <v>133</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E32" s="17" t="n">
         <v>26</v>
@@ -14455,13 +14452,13 @@
         <v>6</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C33" s="16" t="s">
         <v>130</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E33" s="17" t="n">
         <v>65</v>
@@ -14482,13 +14479,13 @@
         <v>6</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E34" s="17" t="n">
         <v>3</v>
@@ -14509,13 +14506,13 @@
         <v>6</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C35" s="16" t="s">
         <v>133</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E35" s="17" t="n">
         <v>99</v>
@@ -14536,13 +14533,13 @@
         <v>6</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C36" s="16" t="s">
         <v>130</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E36" s="17" t="n">
         <v>139</v>
@@ -14563,13 +14560,13 @@
         <v>6</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E37" s="17" t="n">
         <v>7</v>
@@ -14590,13 +14587,13 @@
         <v>6</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C38" s="16" t="s">
         <v>133</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E38" s="17" t="n">
         <v>7</v>
@@ -14617,13 +14614,13 @@
         <v>6</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E39" s="17" t="n">
         <v>2</v>
@@ -14644,13 +14641,13 @@
         <v>6</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C40" s="16" t="s">
         <v>130</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E40" s="17" t="n">
         <v>25</v>
@@ -14671,13 +14668,13 @@
         <v>6</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C41" s="16" t="s">
         <v>133</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E41" s="17" t="n">
         <v>30</v>
@@ -14698,13 +14695,13 @@
         <v>6</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C42" s="16" t="s">
         <v>130</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E42" s="17" t="n">
         <v>52</v>
@@ -14725,13 +14722,13 @@
         <v>6</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C43" s="16" t="s">
         <v>133</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E43" s="17" t="n">
         <v>23</v>
@@ -14752,13 +14749,13 @@
         <v>6</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C44" s="16" t="s">
         <v>130</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E44" s="17" t="n">
         <v>47</v>
@@ -14773,7 +14770,7 @@
         <v>141</v>
       </c>
       <c r="I44" s="18" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14781,13 +14778,13 @@
         <v>6</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C45" s="16" t="s">
         <v>133</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E45" s="17" t="n">
         <v>39</v>
@@ -14808,13 +14805,13 @@
         <v>6</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C46" s="16" t="s">
         <v>130</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E46" s="17" t="n">
         <v>120</v>
@@ -14835,13 +14832,13 @@
         <v>6</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C47" s="16" t="s">
         <v>133</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E47" s="17" t="n">
         <v>2</v>
@@ -14860,13 +14857,13 @@
         <v>6</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C48" s="16" t="s">
         <v>130</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E48" s="17" t="n">
         <v>45</v>
@@ -14879,7 +14876,7 @@
         <v>45</v>
       </c>
       <c r="I48" s="18" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14887,13 +14884,13 @@
         <v>6</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C49" s="16" t="s">
         <v>133</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E49" s="17" t="n">
         <v>13</v>
@@ -14912,13 +14909,13 @@
         <v>6</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C50" s="16" t="s">
         <v>130</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E50" s="17" t="n">
         <v>132</v>
@@ -14937,13 +14934,13 @@
         <v>6</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C51" s="16" t="s">
         <v>130</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E51" s="17" t="n">
         <v>267</v>
@@ -14964,13 +14961,13 @@
         <v>6</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C52" s="16" t="s">
         <v>133</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E52" s="17" t="n">
         <v>31</v>
@@ -14991,13 +14988,13 @@
         <v>6</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C53" s="16" t="s">
         <v>130</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E53" s="17" t="n">
         <v>76</v>
@@ -15016,13 +15013,13 @@
         <v>6</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C54" s="16" t="s">
         <v>133</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E54" s="17" t="n">
         <v>15</v>
@@ -15041,13 +15038,13 @@
         <v>6</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E55" s="17" t="n">
         <v>5</v>
@@ -15066,13 +15063,13 @@
         <v>26</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D56" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E56" s="17" t="n">
         <v>9</v>
@@ -15093,13 +15090,13 @@
         <v>26</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E57" s="17" t="n">
         <v>4</v>
@@ -15120,13 +15117,13 @@
         <v>26</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D58" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E58" s="17" t="n">
         <v>8</v>
@@ -15147,13 +15144,13 @@
         <v>26</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D59" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E59" s="17" t="n">
         <v>21</v>
@@ -15174,13 +15171,13 @@
         <v>26</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E60" s="17" t="n">
         <v>138</v>
@@ -15201,13 +15198,13 @@
         <v>26</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E61" s="17" t="n">
         <v>88</v>
@@ -15228,13 +15225,13 @@
         <v>26</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E62" s="17" t="n">
         <v>5</v>
@@ -15255,13 +15252,13 @@
         <v>26</v>
       </c>
       <c r="B63" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E63" s="17" t="n">
         <v>66</v>
@@ -15282,13 +15279,13 @@
         <v>26</v>
       </c>
       <c r="B64" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E64" s="17" t="n">
         <v>15</v>
@@ -15309,13 +15306,13 @@
         <v>26</v>
       </c>
       <c r="B65" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C65" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E65" s="17" t="n">
         <v>122</v>
@@ -15336,13 +15333,13 @@
         <v>26</v>
       </c>
       <c r="B66" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D66" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E66" s="17" t="n">
         <v>6</v>
@@ -15363,13 +15360,13 @@
         <v>26</v>
       </c>
       <c r="B67" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C67" s="16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D67" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E67" s="17" t="n">
         <v>6</v>
@@ -15384,7 +15381,7 @@
         <v>24</v>
       </c>
       <c r="I67" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15392,13 +15389,13 @@
         <v>26</v>
       </c>
       <c r="B68" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C68" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D68" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E68" s="17" t="n">
         <v>2</v>
@@ -15419,13 +15416,13 @@
         <v>26</v>
       </c>
       <c r="B69" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C69" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D69" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E69" s="17" t="n">
         <v>20</v>
@@ -15446,13 +15443,13 @@
         <v>26</v>
       </c>
       <c r="B70" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D70" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E70" s="17" t="n">
         <v>26</v>
@@ -15473,13 +15470,13 @@
         <v>26</v>
       </c>
       <c r="B71" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C71" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D71" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E71" s="17" t="n">
         <v>36</v>
@@ -15500,13 +15497,13 @@
         <v>26</v>
       </c>
       <c r="B72" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C72" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D72" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E72" s="17" t="n">
         <v>143</v>
@@ -15527,13 +15524,13 @@
         <v>26</v>
       </c>
       <c r="B73" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C73" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D73" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E73" s="17" t="n">
         <v>6</v>
@@ -15554,13 +15551,13 @@
         <v>26</v>
       </c>
       <c r="B74" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D74" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E74" s="17" t="n">
         <v>21</v>
@@ -15581,13 +15578,13 @@
         <v>26</v>
       </c>
       <c r="B75" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D75" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E75" s="17" t="n">
         <v>29</v>
@@ -15608,13 +15605,13 @@
         <v>26</v>
       </c>
       <c r="B76" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C76" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D76" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E76" s="17" t="n">
         <v>133</v>
@@ -15635,13 +15632,13 @@
         <v>26</v>
       </c>
       <c r="B77" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C77" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D77" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E77" s="17" t="n">
         <v>2</v>
@@ -15662,13 +15659,13 @@
         <v>26</v>
       </c>
       <c r="B78" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C78" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D78" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E78" s="17" t="n">
         <v>4</v>
@@ -15689,13 +15686,13 @@
         <v>26</v>
       </c>
       <c r="B79" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C79" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D79" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E79" s="17" t="n">
         <v>20</v>
@@ -15716,13 +15713,13 @@
         <v>26</v>
       </c>
       <c r="B80" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C80" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D80" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E80" s="17" t="n">
         <v>34</v>
@@ -15743,13 +15740,13 @@
         <v>26</v>
       </c>
       <c r="B81" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C81" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D81" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E81" s="17" t="n">
         <v>57</v>
@@ -15768,13 +15765,13 @@
         <v>26</v>
       </c>
       <c r="B82" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C82" s="16" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D82" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E82" s="17" t="n">
         <v>6</v>
@@ -15795,13 +15792,13 @@
         <v>26</v>
       </c>
       <c r="B83" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C83" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E83" s="17" t="n">
         <v>6</v>
@@ -15822,13 +15819,13 @@
         <v>26</v>
       </c>
       <c r="B84" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C84" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D84" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E84" s="17" t="n">
         <v>21</v>
@@ -15849,13 +15846,13 @@
         <v>26</v>
       </c>
       <c r="B85" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C85" s="16" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D85" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E85" s="17" t="n">
         <v>16</v>
@@ -15876,13 +15873,13 @@
         <v>26</v>
       </c>
       <c r="B86" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C86" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D86" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E86" s="17" t="n">
         <v>10</v>
@@ -15903,13 +15900,13 @@
         <v>26</v>
       </c>
       <c r="B87" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C87" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D87" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E87" s="17" t="n">
         <v>23</v>
@@ -15928,13 +15925,13 @@
         <v>26</v>
       </c>
       <c r="B88" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C88" s="16" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D88" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E88" s="17" t="n">
         <v>3</v>
@@ -15953,13 +15950,13 @@
         <v>26</v>
       </c>
       <c r="B89" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C89" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D89" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E89" s="17" t="n">
         <v>16</v>
@@ -15978,13 +15975,13 @@
         <v>26</v>
       </c>
       <c r="B90" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C90" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D90" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E90" s="17" t="n">
         <v>81</v>
@@ -16003,13 +16000,13 @@
         <v>26</v>
       </c>
       <c r="B91" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C91" s="16" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D91" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E91" s="17" t="n">
         <v>2</v>
@@ -16028,13 +16025,13 @@
         <v>26</v>
       </c>
       <c r="B92" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C92" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D92" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E92" s="17" t="n">
         <v>157</v>
@@ -16053,13 +16050,13 @@
         <v>26</v>
       </c>
       <c r="B93" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C93" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D93" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E93" s="17" t="n">
         <v>35</v>
@@ -16078,13 +16075,13 @@
         <v>26</v>
       </c>
       <c r="B94" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C94" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D94" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E94" s="17" t="n">
         <v>82</v>
@@ -16105,13 +16102,13 @@
         <v>26</v>
       </c>
       <c r="B95" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C95" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D95" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E95" s="17" t="n">
         <v>41</v>
@@ -16130,13 +16127,13 @@
         <v>26</v>
       </c>
       <c r="B96" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C96" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D96" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E96" s="17" t="n">
         <v>6</v>
@@ -16155,13 +16152,13 @@
         <v>26</v>
       </c>
       <c r="B97" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C97" s="16" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D97" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E97" s="17" t="n">
         <v>5</v>
@@ -16180,13 +16177,13 @@
         <v>26</v>
       </c>
       <c r="B98" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C98" s="16" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D98" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E98" s="17" t="n">
         <v>1</v>
@@ -16205,13 +16202,13 @@
         <v>26</v>
       </c>
       <c r="B99" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C99" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D99" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E99" s="17" t="n">
         <v>10</v>
@@ -16230,13 +16227,13 @@
         <v>26</v>
       </c>
       <c r="B100" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C100" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D100" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E100" s="17" t="n">
         <v>7</v>
@@ -16255,13 +16252,13 @@
         <v>29</v>
       </c>
       <c r="B101" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C101" s="16" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D101" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E101" s="17" t="n">
         <v>1</v>
@@ -16280,13 +16277,13 @@
         <v>29</v>
       </c>
       <c r="B102" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C102" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D102" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E102" s="17" t="n">
         <v>19</v>
@@ -16307,13 +16304,13 @@
         <v>29</v>
       </c>
       <c r="B103" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C103" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D103" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E103" s="17" t="n">
         <v>11</v>
@@ -16334,13 +16331,13 @@
         <v>29</v>
       </c>
       <c r="B104" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C104" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D104" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E104" s="17" t="n">
         <v>14</v>
@@ -16361,13 +16358,13 @@
         <v>29</v>
       </c>
       <c r="B105" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C105" s="16" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D105" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E105" s="17" t="n">
         <v>3</v>
@@ -16388,13 +16385,13 @@
         <v>29</v>
       </c>
       <c r="B106" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C106" s="16" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D106" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E106" s="17" t="n">
         <v>11</v>
@@ -16415,13 +16412,13 @@
         <v>29</v>
       </c>
       <c r="B107" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C107" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D107" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E107" s="17" t="n">
         <v>25</v>
@@ -16442,13 +16439,13 @@
         <v>29</v>
       </c>
       <c r="B108" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C108" s="16" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D108" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E108" s="17" t="n">
         <v>11</v>
@@ -16469,13 +16466,13 @@
         <v>29</v>
       </c>
       <c r="B109" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C109" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D109" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E109" s="17" t="n">
         <v>19</v>
@@ -16496,13 +16493,13 @@
         <v>29</v>
       </c>
       <c r="B110" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C110" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D110" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E110" s="17" t="n">
         <v>38</v>
@@ -16523,13 +16520,13 @@
         <v>29</v>
       </c>
       <c r="B111" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C111" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D111" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E111" s="17" t="n">
         <v>16</v>
@@ -16544,7 +16541,7 @@
         <v>32</v>
       </c>
       <c r="I111" s="16" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16552,13 +16549,13 @@
         <v>29</v>
       </c>
       <c r="B112" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C112" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D112" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E112" s="17" t="n">
         <v>262</v>
@@ -16579,13 +16576,13 @@
         <v>29</v>
       </c>
       <c r="B113" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C113" s="16" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D113" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E113" s="17" t="n">
         <v>1</v>
@@ -16604,13 +16601,13 @@
         <v>29</v>
       </c>
       <c r="B114" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C114" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D114" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E114" s="17" t="n">
         <v>3</v>
@@ -16631,13 +16628,13 @@
         <v>29</v>
       </c>
       <c r="B115" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C115" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D115" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E115" s="17" t="n">
         <v>3</v>
@@ -16652,7 +16649,7 @@
         <v>9</v>
       </c>
       <c r="I115" s="16" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16660,13 +16657,13 @@
         <v>29</v>
       </c>
       <c r="B116" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C116" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D116" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E116" s="17" t="n">
         <v>35</v>
@@ -16681,7 +16678,7 @@
         <v>70</v>
       </c>
       <c r="I116" s="16" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16689,13 +16686,13 @@
         <v>29</v>
       </c>
       <c r="B117" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C117" s="16" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D117" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E117" s="17" t="n">
         <v>46</v>
@@ -16716,13 +16713,13 @@
         <v>29</v>
       </c>
       <c r="B118" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C118" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D118" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E118" s="17" t="n">
         <v>3</v>
@@ -16737,7 +16734,7 @@
         <v>12</v>
       </c>
       <c r="I118" s="16" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16745,13 +16742,13 @@
         <v>29</v>
       </c>
       <c r="B119" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C119" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D119" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E119" s="17" t="n">
         <v>18</v>
@@ -16766,7 +16763,7 @@
         <v>54</v>
       </c>
       <c r="I119" s="16" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16774,13 +16771,13 @@
         <v>29</v>
       </c>
       <c r="B120" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C120" s="16" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D120" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E120" s="17" t="n">
         <v>146</v>
@@ -16801,13 +16798,13 @@
         <v>29</v>
       </c>
       <c r="B121" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C121" s="16" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D121" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E121" s="17" t="n">
         <v>89</v>
@@ -16828,13 +16825,13 @@
         <v>29</v>
       </c>
       <c r="B122" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C122" s="16" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D122" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E122" s="17" t="n">
         <v>49</v>
@@ -16853,13 +16850,13 @@
         <v>29</v>
       </c>
       <c r="B123" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C123" s="16" t="s">
         <v>122</v>
       </c>
       <c r="D123" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E123" s="17" t="n">
         <v>9</v>
@@ -16878,13 +16875,13 @@
         <v>14</v>
       </c>
       <c r="B124" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C124" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D124" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E124" s="17" t="n">
         <v>4</v>
@@ -16905,13 +16902,13 @@
         <v>14</v>
       </c>
       <c r="B125" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C125" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D125" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E125" s="17" t="n">
         <v>157</v>
@@ -16932,13 +16929,13 @@
         <v>14</v>
       </c>
       <c r="B126" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C126" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D126" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E126" s="17" t="n">
         <v>145</v>
@@ -16959,13 +16956,13 @@
         <v>14</v>
       </c>
       <c r="B127" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C127" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D127" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E127" s="17" t="n">
         <v>229</v>
@@ -16986,13 +16983,13 @@
         <v>14</v>
       </c>
       <c r="B128" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C128" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D128" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E128" s="17" t="n">
         <v>50</v>
@@ -17013,13 +17010,13 @@
         <v>14</v>
       </c>
       <c r="B129" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C129" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D129" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E129" s="17" t="n">
         <v>281</v>
@@ -17040,13 +17037,13 @@
         <v>14</v>
       </c>
       <c r="B130" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C130" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D130" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E130" s="17" t="n">
         <v>39</v>
@@ -17067,13 +17064,13 @@
         <v>14</v>
       </c>
       <c r="B131" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C131" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D131" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E131" s="17" t="n">
         <v>279</v>
@@ -17094,13 +17091,13 @@
         <v>14</v>
       </c>
       <c r="B132" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C132" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D132" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E132" s="17" t="n">
         <v>93</v>
@@ -17121,13 +17118,13 @@
         <v>14</v>
       </c>
       <c r="B133" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C133" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D133" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E133" s="17" t="n">
         <v>567</v>
@@ -17148,13 +17145,13 @@
         <v>14</v>
       </c>
       <c r="B134" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C134" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D134" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E134" s="17" t="n">
         <v>46</v>
@@ -17175,13 +17172,13 @@
         <v>14</v>
       </c>
       <c r="B135" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C135" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D135" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E135" s="17" t="n">
         <v>273</v>
@@ -17202,13 +17199,13 @@
         <v>14</v>
       </c>
       <c r="B136" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C136" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D136" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E136" s="17" t="n">
         <v>86</v>
@@ -17229,13 +17226,13 @@
         <v>14</v>
       </c>
       <c r="B137" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C137" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D137" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E137" s="17" t="n">
         <v>480</v>
@@ -17256,13 +17253,13 @@
         <v>14</v>
       </c>
       <c r="B138" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C138" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D138" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E138" s="17" t="n">
         <v>11</v>
@@ -17280,16 +17277,16 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B139" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C139" s="16" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D139" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E139" s="17" t="n">
         <v>1</v>
@@ -17305,16 +17302,16 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B140" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C140" s="16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D140" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E140" s="17" t="n">
         <v>10</v>
@@ -17332,16 +17329,16 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B141" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C141" s="16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D141" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E141" s="17" t="n">
         <v>78</v>
@@ -17357,16 +17354,16 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B142" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C142" s="16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D142" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E142" s="17" t="n">
         <v>15</v>
@@ -17381,21 +17378,21 @@
         <v>60</v>
       </c>
       <c r="I142" s="16" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B143" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C143" s="16" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D143" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E143" s="17" t="n">
         <v>5</v>
@@ -17411,16 +17408,16 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B144" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C144" s="16" t="s">
         <v>122</v>
       </c>
       <c r="D144" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E144" s="17" t="n">
         <v>11</v>
@@ -17438,16 +17435,16 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B145" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C145" s="16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D145" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E145" s="17" t="n">
         <v>8</v>
@@ -17465,16 +17462,16 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B146" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C146" s="16" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D146" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E146" s="17" t="n">
         <v>1</v>
@@ -17492,16 +17489,16 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B147" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C147" s="16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D147" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E147" s="17" t="n">
         <v>43</v>
@@ -17519,16 +17516,16 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B148" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C148" s="16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D148" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E148" s="17" t="n">
         <v>4</v>
@@ -17546,16 +17543,16 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B149" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C149" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D149" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E149" s="17" t="n">
         <v>248</v>
@@ -17570,21 +17567,21 @@
         <v>744</v>
       </c>
       <c r="I149" s="16" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B150" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C150" s="16" t="s">
         <v>122</v>
       </c>
       <c r="D150" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E150" s="17" t="n">
         <v>46</v>
@@ -17602,16 +17599,16 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B151" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C151" s="16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D151" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E151" s="17" t="n">
         <v>5</v>
@@ -17629,16 +17626,16 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B152" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C152" s="16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D152" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E152" s="17" t="n">
         <v>1</v>
@@ -17656,16 +17653,16 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B153" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C153" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D153" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E153" s="17" t="n">
         <v>18</v>
@@ -17683,16 +17680,16 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B154" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C154" s="16" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D154" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E154" s="17" t="n">
         <v>9</v>
@@ -17710,16 +17707,16 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B155" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C155" s="16" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D155" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E155" s="17" t="n">
         <v>7</v>
@@ -17737,16 +17734,16 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B156" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C156" s="16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D156" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E156" s="17" t="n">
         <v>34</v>
@@ -17764,16 +17761,16 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B157" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C157" s="16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D157" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E157" s="17" t="n">
         <v>2</v>
@@ -17791,16 +17788,16 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B158" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C158" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D158" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E158" s="17" t="n">
         <v>250</v>
@@ -17818,16 +17815,16 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B159" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C159" s="16" t="s">
         <v>122</v>
       </c>
       <c r="D159" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E159" s="17" t="n">
         <v>146</v>
@@ -17845,16 +17842,16 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B160" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C160" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D160" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E160" s="17" t="n">
         <v>12</v>
@@ -17872,16 +17869,16 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B161" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C161" s="16" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D161" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E161" s="17" t="n">
         <v>9</v>
@@ -17899,16 +17896,16 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B162" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C162" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D162" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E162" s="17" t="n">
         <v>150</v>
@@ -17926,16 +17923,16 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B163" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C163" s="16" t="s">
         <v>122</v>
       </c>
       <c r="D163" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E163" s="17" t="n">
         <v>86</v>
@@ -17953,16 +17950,16 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B164" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C164" s="16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D164" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E164" s="17" t="n">
         <v>25</v>
@@ -17980,16 +17977,16 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B165" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C165" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D165" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E165" s="17" t="n">
         <v>52</v>
@@ -18007,16 +18004,16 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B166" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C166" s="16" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D166" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E166" s="17" t="n">
         <v>6</v>
@@ -18034,16 +18031,16 @@
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B167" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C167" s="16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D167" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E167" s="17" t="n">
         <v>11</v>
@@ -18061,16 +18058,16 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B168" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C168" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D168" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E168" s="17" t="n">
         <v>194</v>
@@ -18088,16 +18085,16 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B169" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C169" s="16" t="s">
         <v>122</v>
       </c>
       <c r="D169" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E169" s="17" t="n">
         <v>46</v>
@@ -18115,16 +18112,16 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B170" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C170" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D170" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E170" s="17" t="n">
         <v>33</v>
@@ -18142,16 +18139,16 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B171" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C171" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D171" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E171" s="17" t="n">
         <v>67</v>
@@ -18169,16 +18166,16 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B172" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C172" s="16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D172" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E172" s="17" t="n">
         <v>15</v>
@@ -18194,16 +18191,16 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B173" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C173" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D173" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E173" s="17" t="n">
         <v>194</v>
@@ -18221,16 +18218,16 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B174" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C174" s="16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D174" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E174" s="17" t="n">
         <v>3</v>
@@ -18246,16 +18243,16 @@
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B175" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C175" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D175" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E175" s="17" t="n">
         <v>32</v>
@@ -18271,16 +18268,16 @@
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B176" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C176" s="16" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D176" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E176" s="17" t="n">
         <v>6</v>
@@ -18296,16 +18293,16 @@
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="16" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B177" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C177" s="16" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D177" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E177" s="17" t="n">
         <v>8</v>
@@ -18323,16 +18320,16 @@
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="16" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B178" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C178" s="16" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D178" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E178" s="17" t="n">
         <v>31</v>
@@ -18350,16 +18347,16 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="16" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B179" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C179" s="16" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D179" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E179" s="17" t="n">
         <v>82</v>
@@ -18377,16 +18374,16 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="16" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B180" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C180" s="16" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D180" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E180" s="17" t="n">
         <v>16</v>
@@ -18404,16 +18401,16 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="16" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B181" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C181" s="16" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D181" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E181" s="17" t="n">
         <v>8</v>
@@ -18431,16 +18428,16 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="16" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B182" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C182" s="16" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D182" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E182" s="17" t="n">
         <v>24</v>
@@ -18458,16 +18455,16 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="16" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B183" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C183" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D183" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E183" s="17" t="n">
         <v>47</v>
@@ -18485,16 +18482,16 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="16" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B184" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C184" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D184" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E184" s="17" t="n">
         <v>293</v>
@@ -18512,16 +18509,16 @@
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="16" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B185" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C185" s="16" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D185" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E185" s="17" t="n">
         <v>367</v>
@@ -18539,16 +18536,16 @@
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="16" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B186" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C186" s="16" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D186" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E186" s="17" t="n">
         <v>244</v>
@@ -18564,16 +18561,16 @@
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="16" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B187" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C187" s="16" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D187" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E187" s="17" t="n">
         <v>73</v>
@@ -18622,25 +18619,25 @@
         <v>90</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>322</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>323</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>6</v>
@@ -18664,31 +18661,31 @@
         <v>18</v>
       </c>
       <c r="P1" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q1" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>331</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>332</v>
       </c>
       <c r="Y1" s="3" t="s">
         <v>214</v>
@@ -18699,19 +18696,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="C2" s="18" t="s">
         <v>333</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="D2" s="16" t="s">
         <v>334</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="E2" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="F2" s="18" t="s">
         <v>336</v>
-      </c>
-      <c r="F2" s="18" t="s">
-        <v>337</v>
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="7" t="n">
@@ -18745,19 +18742,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="C3" s="18" t="s">
         <v>333</v>
       </c>
-      <c r="C3" s="18" t="s">
-        <v>334</v>
-      </c>
       <c r="D3" s="18" t="s">
+        <v>337</v>
+      </c>
+      <c r="E3" s="18" t="s">
         <v>338</v>
       </c>
-      <c r="E3" s="18" t="s">
-        <v>339</v>
-      </c>
       <c r="F3" s="18" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
@@ -18787,19 +18784,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="C4" s="18" t="s">
         <v>333</v>
       </c>
-      <c r="C4" s="18" t="s">
-        <v>334</v>
-      </c>
       <c r="D4" s="18" t="s">
+        <v>339</v>
+      </c>
+      <c r="E4" s="18" t="s">
         <v>340</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="F4" s="18" t="s">
         <v>341</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>342</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>0.01</v>
@@ -18833,19 +18830,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="C5" s="18" t="s">
         <v>333</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>334</v>
-      </c>
       <c r="D5" s="18" t="s">
+        <v>342</v>
+      </c>
+      <c r="E5" s="18" t="s">
         <v>343</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="F5" s="18" t="s">
         <v>344</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>345</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>0.07</v>
@@ -18879,17 +18876,17 @@
         <v>5</v>
       </c>
       <c r="B6" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="C6" s="18" t="s">
         <v>333</v>
       </c>
-      <c r="C6" s="18" t="s">
-        <v>334</v>
-      </c>
       <c r="D6" s="18" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E6" s="16"/>
       <c r="F6" s="18" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>0.02</v>
@@ -18923,17 +18920,17 @@
         <v>6</v>
       </c>
       <c r="B7" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="C7" s="18" t="s">
         <v>333</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>334</v>
-      </c>
       <c r="D7" s="16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E7" s="16"/>
       <c r="F7" s="18" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>0.02</v>
@@ -18967,17 +18964,17 @@
         <v>7</v>
       </c>
       <c r="B8" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="C8" s="18" t="s">
         <v>333</v>
       </c>
-      <c r="C8" s="18" t="s">
-        <v>334</v>
-      </c>
       <c r="D8" s="18" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E8" s="16"/>
       <c r="F8" s="18" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>0.02</v>
@@ -19011,19 +19008,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C9" s="16" t="s">
+        <v>348</v>
+      </c>
+      <c r="D9" s="18" t="s">
         <v>349</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="E9" s="18" t="s">
         <v>350</v>
       </c>
-      <c r="E9" s="18" t="s">
-        <v>351</v>
-      </c>
       <c r="F9" s="18" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="7" t="n">
@@ -19057,17 +19054,17 @@
         <v>9</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E10" s="16"/>
       <c r="F10" s="18" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>0.01</v>
@@ -19103,19 +19100,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C11" s="18" t="s">
+        <v>352</v>
+      </c>
+      <c r="D11" s="18" t="s">
         <v>353</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="E11" s="18" t="s">
         <v>354</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="F11" s="18" t="s">
         <v>355</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>356</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>0.02</v>
@@ -19153,19 +19150,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D12" s="18" t="s">
+        <v>356</v>
+      </c>
+      <c r="E12" s="18" t="s">
         <v>357</v>
       </c>
-      <c r="E12" s="18" t="s">
-        <v>358</v>
-      </c>
       <c r="F12" s="18" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>0.05</v>
@@ -19209,19 +19206,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D13" s="18" t="s">
+        <v>358</v>
+      </c>
+      <c r="E13" s="18" t="s">
         <v>359</v>
       </c>
-      <c r="E13" s="18" t="s">
-        <v>360</v>
-      </c>
       <c r="F13" s="18" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>0.05</v>
@@ -19255,19 +19252,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="18" t="s">
+        <v>360</v>
+      </c>
+      <c r="C14" s="18" t="s">
         <v>361</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="D14" s="18" t="s">
         <v>362</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="E14" s="18" t="s">
         <v>363</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="F14" s="18" t="s">
         <v>364</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>365</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
@@ -19299,19 +19296,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="18" t="s">
+        <v>360</v>
+      </c>
+      <c r="C15" s="18" t="s">
         <v>361</v>
       </c>
-      <c r="C15" s="18" t="s">
-        <v>362</v>
-      </c>
       <c r="D15" s="18" t="s">
+        <v>365</v>
+      </c>
+      <c r="E15" s="18" t="s">
         <v>366</v>
       </c>
-      <c r="E15" s="18" t="s">
-        <v>367</v>
-      </c>
       <c r="F15" s="18" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
@@ -19343,19 +19340,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="18" t="s">
+        <v>360</v>
+      </c>
+      <c r="C16" s="18" t="s">
         <v>361</v>
       </c>
-      <c r="C16" s="18" t="s">
-        <v>362</v>
-      </c>
       <c r="D16" s="18" t="s">
+        <v>367</v>
+      </c>
+      <c r="E16" s="16" t="s">
         <v>368</v>
       </c>
-      <c r="E16" s="16" t="s">
-        <v>369</v>
-      </c>
       <c r="F16" s="18" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
@@ -19387,19 +19384,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="18" t="s">
+        <v>360</v>
+      </c>
+      <c r="C17" s="18" t="s">
         <v>361</v>
       </c>
-      <c r="C17" s="18" t="s">
-        <v>362</v>
-      </c>
       <c r="D17" s="18" t="s">
+        <v>369</v>
+      </c>
+      <c r="E17" s="18" t="s">
         <v>370</v>
       </c>
-      <c r="E17" s="18" t="s">
-        <v>371</v>
-      </c>
       <c r="F17" s="18" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
@@ -19431,19 +19428,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="18" t="s">
+        <v>360</v>
+      </c>
+      <c r="C18" s="18" t="s">
         <v>361</v>
       </c>
-      <c r="C18" s="18" t="s">
-        <v>362</v>
-      </c>
       <c r="D18" s="18" t="s">
+        <v>371</v>
+      </c>
+      <c r="E18" s="18" t="s">
         <v>372</v>
       </c>
-      <c r="E18" s="18" t="s">
-        <v>373</v>
-      </c>
       <c r="F18" s="18" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
@@ -19475,19 +19472,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="C19" s="18" t="s">
         <v>374</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="D19" s="18" t="s">
         <v>375</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="E19" s="18" t="s">
         <v>376</v>
       </c>
-      <c r="E19" s="18" t="s">
-        <v>377</v>
-      </c>
       <c r="F19" s="18" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>0.02</v>
@@ -19521,19 +19518,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="C20" s="18" t="s">
         <v>374</v>
       </c>
-      <c r="C20" s="18" t="s">
-        <v>375</v>
-      </c>
       <c r="D20" s="18" t="s">
+        <v>377</v>
+      </c>
+      <c r="E20" s="16" t="s">
         <v>378</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="F20" s="18" t="s">
         <v>379</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>380</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="7" t="n">
@@ -19579,19 +19576,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="C21" s="18" t="s">
         <v>374</v>
       </c>
-      <c r="C21" s="18" t="s">
-        <v>375</v>
-      </c>
       <c r="D21" s="18" t="s">
+        <v>380</v>
+      </c>
+      <c r="E21" s="18" t="s">
         <v>381</v>
       </c>
-      <c r="E21" s="18" t="s">
-        <v>382</v>
-      </c>
       <c r="F21" s="18" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>0.02</v>
@@ -19625,19 +19622,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="C22" s="18" t="s">
         <v>374</v>
       </c>
-      <c r="C22" s="18" t="s">
-        <v>375</v>
-      </c>
       <c r="D22" s="18" t="s">
+        <v>382</v>
+      </c>
+      <c r="E22" s="18" t="s">
         <v>383</v>
       </c>
-      <c r="E22" s="18" t="s">
-        <v>384</v>
-      </c>
       <c r="F22" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G22" s="7"/>
       <c r="H22" s="7" t="n">
@@ -19683,19 +19680,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="C23" s="18" t="s">
         <v>374</v>
       </c>
-      <c r="C23" s="18" t="s">
-        <v>375</v>
-      </c>
       <c r="D23" s="18" t="s">
+        <v>384</v>
+      </c>
+      <c r="E23" s="18" t="s">
         <v>385</v>
       </c>
-      <c r="E23" s="18" t="s">
-        <v>386</v>
-      </c>
       <c r="F23" s="18" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>0.02</v>
@@ -19737,19 +19734,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C24" s="18" t="s">
+        <v>386</v>
+      </c>
+      <c r="D24" s="18" t="s">
         <v>387</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="E24" s="18" t="s">
         <v>388</v>
       </c>
-      <c r="E24" s="18" t="s">
-        <v>389</v>
-      </c>
       <c r="F24" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
@@ -19795,19 +19792,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D25" s="18" t="s">
+        <v>389</v>
+      </c>
+      <c r="E25" s="18" t="s">
         <v>390</v>
       </c>
-      <c r="E25" s="18" t="s">
-        <v>391</v>
-      </c>
       <c r="F25" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>0.02</v>
@@ -19853,19 +19850,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D26" s="18" t="s">
+        <v>391</v>
+      </c>
+      <c r="E26" s="18" t="s">
         <v>392</v>
       </c>
-      <c r="E26" s="18" t="s">
-        <v>393</v>
-      </c>
       <c r="F26" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>0.01</v>
@@ -19913,19 +19910,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D27" s="18" t="s">
+        <v>393</v>
+      </c>
+      <c r="E27" s="18" t="s">
         <v>394</v>
       </c>
-      <c r="E27" s="18" t="s">
-        <v>395</v>
-      </c>
       <c r="F27" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G27" s="7"/>
       <c r="H27" s="7"/>
@@ -19969,19 +19966,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D28" s="18" t="s">
+        <v>395</v>
+      </c>
+      <c r="E28" s="18" t="s">
         <v>396</v>
       </c>
-      <c r="E28" s="18" t="s">
-        <v>397</v>
-      </c>
       <c r="F28" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
@@ -20027,19 +20024,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D29" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="E29" s="18" t="s">
         <v>398</v>
       </c>
-      <c r="E29" s="18" t="s">
-        <v>399</v>
-      </c>
       <c r="F29" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
@@ -20083,19 +20080,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D30" s="18" t="s">
+        <v>399</v>
+      </c>
+      <c r="E30" s="18" t="s">
         <v>400</v>
       </c>
-      <c r="E30" s="18" t="s">
-        <v>401</v>
-      </c>
       <c r="F30" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
@@ -20139,19 +20136,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D31" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="E31" s="18" t="s">
         <v>402</v>
       </c>
-      <c r="E31" s="18" t="s">
+      <c r="F31" s="18" t="s">
         <v>403</v>
-      </c>
-      <c r="F31" s="18" t="s">
-        <v>404</v>
       </c>
       <c r="G31" s="7"/>
       <c r="H31" s="7"/>
@@ -20185,19 +20182,19 @@
         <v>31</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D32" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="E32" s="18" t="s">
         <v>405</v>
       </c>
-      <c r="E32" s="18" t="s">
-        <v>406</v>
-      </c>
       <c r="F32" s="18" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>0.01</v>
@@ -20235,19 +20232,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D33" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="E33" s="18" t="s">
         <v>407</v>
       </c>
-      <c r="E33" s="18" t="s">
-        <v>408</v>
-      </c>
       <c r="F33" s="18" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
@@ -20283,19 +20280,19 @@
         <v>33</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D34" s="18" t="s">
+        <v>408</v>
+      </c>
+      <c r="E34" s="18" t="s">
         <v>409</v>
       </c>
-      <c r="E34" s="18" t="s">
-        <v>410</v>
-      </c>
       <c r="F34" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G34" s="7"/>
       <c r="H34" s="7"/>
@@ -20327,19 +20324,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D35" s="18" t="s">
+        <v>410</v>
+      </c>
+      <c r="E35" s="18" t="s">
         <v>411</v>
       </c>
-      <c r="E35" s="18" t="s">
-        <v>412</v>
-      </c>
       <c r="F35" s="18" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
@@ -20383,19 +20380,19 @@
         <v>35</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D36" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="E36" s="18" t="s">
         <v>413</v>
       </c>
-      <c r="E36" s="18" t="s">
-        <v>414</v>
-      </c>
       <c r="F36" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
@@ -20427,19 +20424,19 @@
         <v>36</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D37" s="18" t="s">
+        <v>414</v>
+      </c>
+      <c r="E37" s="18" t="s">
         <v>415</v>
       </c>
-      <c r="E37" s="18" t="s">
-        <v>416</v>
-      </c>
       <c r="F37" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G37" s="7"/>
       <c r="H37" s="7"/>
@@ -20471,19 +20468,19 @@
         <v>37</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D38" s="18" t="s">
+        <v>416</v>
+      </c>
+      <c r="E38" s="18" t="s">
         <v>417</v>
       </c>
-      <c r="E38" s="18" t="s">
-        <v>418</v>
-      </c>
       <c r="F38" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
@@ -20519,19 +20516,19 @@
         <v>38</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D39" s="18" t="s">
+        <v>418</v>
+      </c>
+      <c r="E39" s="18" t="s">
         <v>419</v>
       </c>
-      <c r="E39" s="18" t="s">
-        <v>420</v>
-      </c>
       <c r="F39" s="18" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>0.01</v>
@@ -20565,19 +20562,19 @@
         <v>39</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D40" s="18" t="s">
+        <v>420</v>
+      </c>
+      <c r="E40" s="18" t="s">
         <v>421</v>
       </c>
-      <c r="E40" s="18" t="s">
-        <v>422</v>
-      </c>
       <c r="F40" s="18" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
@@ -20625,19 +20622,19 @@
         <v>40</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C41" s="18" t="s">
+        <v>422</v>
+      </c>
+      <c r="D41" s="18" t="s">
         <v>423</v>
       </c>
-      <c r="D41" s="18" t="s">
+      <c r="E41" s="18" t="s">
         <v>424</v>
       </c>
-      <c r="E41" s="18" t="s">
-        <v>425</v>
-      </c>
       <c r="F41" s="18" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
@@ -20681,19 +20678,19 @@
         <v>41</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D42" s="18" t="s">
+        <v>425</v>
+      </c>
+      <c r="E42" s="18" t="s">
         <v>426</v>
       </c>
-      <c r="E42" s="18" t="s">
-        <v>427</v>
-      </c>
       <c r="F42" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G42" s="7"/>
       <c r="H42" s="7"/>
@@ -20737,19 +20734,19 @@
         <v>42</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D43" s="18" t="s">
+        <v>427</v>
+      </c>
+      <c r="E43" s="18" t="s">
         <v>428</v>
       </c>
-      <c r="E43" s="18" t="s">
-        <v>429</v>
-      </c>
       <c r="F43" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G43" s="7"/>
       <c r="H43" s="7"/>
@@ -20793,19 +20790,19 @@
         <v>43</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D44" s="18" t="s">
+        <v>429</v>
+      </c>
+      <c r="E44" s="18" t="s">
         <v>430</v>
       </c>
-      <c r="E44" s="18" t="s">
-        <v>431</v>
-      </c>
       <c r="F44" s="18" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
@@ -20849,19 +20846,19 @@
         <v>44</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C45" s="18" t="s">
+        <v>431</v>
+      </c>
+      <c r="D45" s="18" t="s">
         <v>432</v>
       </c>
-      <c r="D45" s="18" t="s">
+      <c r="E45" s="18" t="s">
         <v>433</v>
       </c>
-      <c r="E45" s="18" t="s">
-        <v>434</v>
-      </c>
       <c r="F45" s="18" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G45" s="7"/>
       <c r="H45" s="7"/>
@@ -20905,19 +20902,19 @@
         <v>45</v>
       </c>
       <c r="B46" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D46" s="18" t="s">
+        <v>434</v>
+      </c>
+      <c r="E46" s="18" t="s">
         <v>435</v>
       </c>
-      <c r="E46" s="18" t="s">
-        <v>436</v>
-      </c>
       <c r="F46" s="18" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G46" s="7"/>
       <c r="H46" s="7"/>
@@ -20967,19 +20964,19 @@
         <v>46</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C47" s="16" t="s">
+        <v>436</v>
+      </c>
+      <c r="D47" s="18" t="s">
         <v>437</v>
       </c>
-      <c r="D47" s="18" t="s">
+      <c r="E47" s="18" t="s">
         <v>438</v>
       </c>
-      <c r="E47" s="18" t="s">
-        <v>439</v>
-      </c>
       <c r="F47" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G47" s="7"/>
       <c r="H47" s="7"/>
@@ -21013,19 +21010,19 @@
         <v>47</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D48" s="18" t="s">
+        <v>439</v>
+      </c>
+      <c r="E48" s="18" t="s">
         <v>440</v>
       </c>
-      <c r="E48" s="18" t="s">
-        <v>441</v>
-      </c>
       <c r="F48" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G48" s="7"/>
       <c r="H48" s="7"/>
@@ -21059,19 +21056,19 @@
         <v>48</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D49" s="18" t="s">
+        <v>441</v>
+      </c>
+      <c r="E49" s="18" t="s">
         <v>442</v>
       </c>
-      <c r="E49" s="18" t="s">
-        <v>443</v>
-      </c>
       <c r="F49" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G49" s="7"/>
       <c r="H49" s="7"/>
@@ -21105,19 +21102,19 @@
         <v>49</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C50" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="D50" s="18" t="s">
         <v>444</v>
       </c>
-      <c r="D50" s="18" t="s">
+      <c r="E50" s="16" t="s">
         <v>445</v>
       </c>
-      <c r="E50" s="16" t="s">
-        <v>446</v>
-      </c>
       <c r="F50" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
@@ -21161,19 +21158,19 @@
         <v>50</v>
       </c>
       <c r="B51" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E51" s="18" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F51" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G51" s="7"/>
       <c r="H51" s="7"/>
@@ -21219,19 +21216,19 @@
         <v>51</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D52" s="18" t="s">
+        <v>447</v>
+      </c>
+      <c r="E52" s="18" t="s">
         <v>448</v>
       </c>
-      <c r="E52" s="18" t="s">
-        <v>449</v>
-      </c>
       <c r="F52" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G52" s="7"/>
       <c r="H52" s="7"/>
@@ -21277,19 +21274,19 @@
         <v>52</v>
       </c>
       <c r="B53" s="18" t="s">
+        <v>449</v>
+      </c>
+      <c r="C53" s="18" t="s">
         <v>450</v>
       </c>
-      <c r="C53" s="18" t="s">
+      <c r="D53" s="18" t="s">
         <v>451</v>
       </c>
-      <c r="D53" s="18" t="s">
+      <c r="E53" s="18" t="s">
         <v>452</v>
       </c>
-      <c r="E53" s="18" t="s">
-        <v>453</v>
-      </c>
       <c r="F53" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G53" s="7"/>
       <c r="H53" s="7"/>
@@ -21333,19 +21330,19 @@
         <v>53</v>
       </c>
       <c r="B54" s="18" t="s">
+        <v>449</v>
+      </c>
+      <c r="C54" s="18" t="s">
         <v>450</v>
       </c>
-      <c r="C54" s="18" t="s">
-        <v>451</v>
-      </c>
       <c r="D54" s="18" t="s">
+        <v>453</v>
+      </c>
+      <c r="E54" s="18" t="s">
         <v>454</v>
       </c>
-      <c r="E54" s="18" t="s">
-        <v>455</v>
-      </c>
       <c r="F54" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
@@ -21389,19 +21386,19 @@
         <v>54</v>
       </c>
       <c r="B55" s="18" t="s">
+        <v>449</v>
+      </c>
+      <c r="C55" s="18" t="s">
         <v>450</v>
       </c>
-      <c r="C55" s="18" t="s">
-        <v>451</v>
-      </c>
       <c r="D55" s="18" t="s">
+        <v>455</v>
+      </c>
+      <c r="E55" s="18" t="s">
         <v>456</v>
       </c>
-      <c r="E55" s="18" t="s">
-        <v>457</v>
-      </c>
       <c r="F55" s="18" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G55" s="7" t="n">
         <v>0.02</v>
@@ -21459,19 +21456,19 @@
         <v>55</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D56" s="18" t="s">
+        <v>457</v>
+      </c>
+      <c r="E56" s="18" t="s">
         <v>458</v>
       </c>
-      <c r="E56" s="18" t="s">
-        <v>459</v>
-      </c>
       <c r="F56" s="18" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
@@ -21515,19 +21512,19 @@
         <v>56</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D57" s="18" t="s">
+        <v>459</v>
+      </c>
+      <c r="E57" s="18" t="s">
         <v>460</v>
       </c>
-      <c r="E57" s="18" t="s">
-        <v>461</v>
-      </c>
       <c r="F57" s="18" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="7"/>
@@ -21571,19 +21568,19 @@
         <v>57</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D58" s="18" t="s">
+        <v>461</v>
+      </c>
+      <c r="E58" s="18" t="s">
         <v>462</v>
       </c>
-      <c r="E58" s="18" t="s">
-        <v>463</v>
-      </c>
       <c r="F58" s="18" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G58" s="7"/>
       <c r="H58" s="7"/>
@@ -21627,19 +21624,19 @@
         <v>58</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D59" s="18" t="s">
+        <v>463</v>
+      </c>
+      <c r="E59" s="18" t="s">
         <v>464</v>
       </c>
-      <c r="E59" s="18" t="s">
-        <v>465</v>
-      </c>
       <c r="F59" s="18" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G59" s="7" t="n">
         <v>0.01</v>
@@ -21689,19 +21686,19 @@
         <v>59</v>
       </c>
       <c r="B60" s="18" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C60" s="18" t="s">
+        <v>465</v>
+      </c>
+      <c r="D60" s="18" t="s">
         <v>466</v>
       </c>
-      <c r="D60" s="18" t="s">
+      <c r="E60" s="16" t="s">
         <v>467</v>
       </c>
-      <c r="E60" s="16" t="s">
-        <v>468</v>
-      </c>
       <c r="F60" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
@@ -21745,19 +21742,19 @@
         <v>60</v>
       </c>
       <c r="B61" s="18" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C61" s="18" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D61" s="18" t="s">
+        <v>399</v>
+      </c>
+      <c r="E61" s="18" t="s">
         <v>400</v>
       </c>
-      <c r="E61" s="18" t="s">
-        <v>401</v>
-      </c>
       <c r="F61" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G61" s="7"/>
       <c r="H61" s="7"/>
@@ -21803,19 +21800,19 @@
         <v>61</v>
       </c>
       <c r="B62" s="18" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D62" s="18" t="s">
+        <v>468</v>
+      </c>
+      <c r="E62" s="18" t="s">
         <v>469</v>
       </c>
-      <c r="E62" s="18" t="s">
-        <v>470</v>
-      </c>
       <c r="F62" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G62" s="7"/>
       <c r="H62" s="7"/>
@@ -21859,19 +21856,19 @@
         <v>62</v>
       </c>
       <c r="B63" s="18" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E63" s="18" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F63" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
@@ -21905,19 +21902,19 @@
         <v>63</v>
       </c>
       <c r="B64" s="18" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D64" s="18" t="s">
+        <v>471</v>
+      </c>
+      <c r="E64" s="18" t="s">
         <v>472</v>
       </c>
-      <c r="E64" s="18" t="s">
-        <v>473</v>
-      </c>
       <c r="F64" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G64" s="7" t="n">
         <v>0.1</v>
@@ -21951,19 +21948,19 @@
         <v>64</v>
       </c>
       <c r="B65" s="18" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C65" s="18" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D65" s="18" t="s">
+        <v>473</v>
+      </c>
+      <c r="E65" s="18" t="s">
         <v>474</v>
       </c>
-      <c r="E65" s="18" t="s">
-        <v>475</v>
-      </c>
       <c r="F65" s="18" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G65" s="7" t="n">
         <v>0.02</v>
@@ -22005,19 +22002,19 @@
         <v>65</v>
       </c>
       <c r="B66" s="18" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C66" s="18" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D66" s="18" t="s">
+        <v>475</v>
+      </c>
+      <c r="E66" s="18" t="s">
         <v>476</v>
       </c>
-      <c r="E66" s="18" t="s">
-        <v>477</v>
-      </c>
       <c r="F66" s="18" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G66" s="7" t="n">
         <v>0.01</v>
@@ -22061,19 +22058,19 @@
         <v>66</v>
       </c>
       <c r="B67" s="18" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C67" s="18" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D67" s="18" t="s">
+        <v>477</v>
+      </c>
+      <c r="E67" s="18" t="s">
         <v>478</v>
       </c>
-      <c r="E67" s="18" t="s">
-        <v>479</v>
-      </c>
       <c r="F67" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G67" s="7"/>
       <c r="H67" s="7"/>
@@ -22111,19 +22108,19 @@
         <v>67</v>
       </c>
       <c r="B68" s="18" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C68" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="D68" s="18" t="s">
         <v>480</v>
       </c>
-      <c r="D68" s="18" t="s">
+      <c r="E68" s="18" t="s">
         <v>481</v>
       </c>
-      <c r="E68" s="18" t="s">
-        <v>482</v>
-      </c>
       <c r="F68" s="18" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G68" s="7"/>
       <c r="H68" s="7"/>
@@ -22163,19 +22160,19 @@
         <v>68</v>
       </c>
       <c r="B69" s="18" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C69" s="18" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D69" s="18" t="s">
+        <v>482</v>
+      </c>
+      <c r="E69" s="18" t="s">
         <v>483</v>
       </c>
-      <c r="E69" s="18" t="s">
-        <v>484</v>
-      </c>
       <c r="F69" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G69" s="7"/>
       <c r="H69" s="7"/>
@@ -22215,19 +22212,19 @@
         <v>69</v>
       </c>
       <c r="B70" s="18" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C70" s="18" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D70" s="18" t="s">
+        <v>484</v>
+      </c>
+      <c r="E70" s="18" t="s">
         <v>485</v>
       </c>
-      <c r="E70" s="18" t="s">
-        <v>486</v>
-      </c>
       <c r="F70" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
@@ -22267,19 +22264,19 @@
         <v>70</v>
       </c>
       <c r="B71" s="18" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D71" s="18" t="s">
+        <v>486</v>
+      </c>
+      <c r="E71" s="18" t="s">
         <v>487</v>
       </c>
-      <c r="E71" s="18" t="s">
-        <v>488</v>
-      </c>
       <c r="F71" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="7"/>
@@ -22319,19 +22316,19 @@
         <v>71</v>
       </c>
       <c r="B72" s="18" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C72" s="18" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D72" s="18" t="s">
+        <v>488</v>
+      </c>
+      <c r="E72" s="18" t="s">
         <v>489</v>
       </c>
-      <c r="E72" s="18" t="s">
-        <v>490</v>
-      </c>
       <c r="F72" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G72" s="7"/>
       <c r="H72" s="7"/>
@@ -22375,19 +22372,19 @@
         <v>72</v>
       </c>
       <c r="B73" s="18" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D73" s="18" t="s">
+        <v>490</v>
+      </c>
+      <c r="E73" s="18" t="s">
         <v>491</v>
       </c>
-      <c r="E73" s="18" t="s">
-        <v>492</v>
-      </c>
       <c r="F73" s="18" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G73" s="7"/>
       <c r="H73" s="7"/>
@@ -22427,19 +22424,19 @@
         <v>73</v>
       </c>
       <c r="B74" s="18" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D74" s="18" t="s">
+        <v>492</v>
+      </c>
+      <c r="E74" s="18" t="s">
         <v>493</v>
       </c>
-      <c r="E74" s="18" t="s">
-        <v>494</v>
-      </c>
       <c r="F74" s="18" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="7"/>
@@ -22479,19 +22476,19 @@
         <v>74</v>
       </c>
       <c r="B75" s="18" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C75" s="18" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D75" s="18" t="s">
+        <v>494</v>
+      </c>
+      <c r="E75" s="18" t="s">
         <v>495</v>
       </c>
-      <c r="E75" s="18" t="s">
-        <v>496</v>
-      </c>
       <c r="F75" s="18" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G75" s="7" t="n">
         <v>0.01</v>
@@ -22539,19 +22536,19 @@
         <v>75</v>
       </c>
       <c r="B76" s="18" t="s">
+        <v>496</v>
+      </c>
+      <c r="C76" s="18" t="s">
+        <v>496</v>
+      </c>
+      <c r="D76" s="16" t="s">
         <v>497</v>
       </c>
-      <c r="C76" s="18" t="s">
-        <v>497</v>
-      </c>
-      <c r="D76" s="16" t="s">
+      <c r="E76" s="18" t="s">
         <v>498</v>
       </c>
-      <c r="E76" s="18" t="s">
-        <v>499</v>
-      </c>
       <c r="F76" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G76" s="7"/>
       <c r="H76" s="7"/>
@@ -22583,19 +22580,19 @@
         <v>76</v>
       </c>
       <c r="B77" s="18" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D77" s="18" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E77" s="18" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F77" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G77" s="7"/>
       <c r="H77" s="7"/>
@@ -22627,19 +22624,19 @@
         <v>77</v>
       </c>
       <c r="B78" s="18" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D78" s="18" t="s">
+        <v>500</v>
+      </c>
+      <c r="E78" s="18" t="s">
         <v>501</v>
       </c>
-      <c r="E78" s="18" t="s">
-        <v>502</v>
-      </c>
       <c r="F78" s="18" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G78" s="7" t="n">
         <v>0.01</v>
@@ -22673,19 +22670,19 @@
         <v>78</v>
       </c>
       <c r="B79" s="18" t="s">
+        <v>502</v>
+      </c>
+      <c r="C79" s="18" t="s">
         <v>503</v>
       </c>
-      <c r="C79" s="18" t="s">
+      <c r="D79" s="18" t="s">
         <v>504</v>
       </c>
-      <c r="D79" s="18" t="s">
+      <c r="E79" s="18" t="s">
         <v>505</v>
       </c>
-      <c r="E79" s="18" t="s">
-        <v>506</v>
-      </c>
       <c r="F79" s="18" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="7"/>
@@ -22715,19 +22712,19 @@
         <v>79</v>
       </c>
       <c r="B80" s="18" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C80" s="18" t="s">
+        <v>506</v>
+      </c>
+      <c r="D80" s="18" t="s">
         <v>507</v>
       </c>
-      <c r="D80" s="18" t="s">
-        <v>508</v>
-      </c>
       <c r="E80" s="18" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F80" s="18" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
@@ -22757,19 +22754,19 @@
         <v>80</v>
       </c>
       <c r="B81" s="18" t="s">
+        <v>508</v>
+      </c>
+      <c r="C81" s="18" t="s">
         <v>509</v>
       </c>
-      <c r="C81" s="18" t="s">
+      <c r="D81" s="18" t="s">
         <v>510</v>
       </c>
-      <c r="D81" s="18" t="s">
+      <c r="E81" s="18" t="s">
         <v>511</v>
       </c>
-      <c r="E81" s="18" t="s">
-        <v>512</v>
-      </c>
       <c r="F81" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G81" s="7"/>
       <c r="H81" s="7" t="n">
@@ -22821,19 +22818,19 @@
         <v>81</v>
       </c>
       <c r="B82" s="18" t="s">
+        <v>508</v>
+      </c>
+      <c r="C82" s="18" t="s">
         <v>509</v>
       </c>
-      <c r="C82" s="18" t="s">
-        <v>510</v>
-      </c>
       <c r="D82" s="18" t="s">
+        <v>512</v>
+      </c>
+      <c r="E82" s="18" t="s">
         <v>513</v>
       </c>
-      <c r="E82" s="18" t="s">
-        <v>514</v>
-      </c>
       <c r="F82" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G82" s="7" t="n">
         <v>0.02</v>
@@ -22897,19 +22894,19 @@
         <v>82</v>
       </c>
       <c r="B83" s="18" t="s">
+        <v>508</v>
+      </c>
+      <c r="C83" s="18" t="s">
         <v>509</v>
       </c>
-      <c r="C83" s="18" t="s">
-        <v>510</v>
-      </c>
       <c r="D83" s="18" t="s">
+        <v>514</v>
+      </c>
+      <c r="E83" s="18" t="s">
         <v>515</v>
       </c>
-      <c r="E83" s="18" t="s">
-        <v>516</v>
-      </c>
       <c r="F83" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G83" s="7" t="n">
         <v>0.01</v>
@@ -22957,19 +22954,19 @@
         <v>83</v>
       </c>
       <c r="B84" s="18" t="s">
+        <v>508</v>
+      </c>
+      <c r="C84" s="18" t="s">
         <v>509</v>
       </c>
-      <c r="C84" s="18" t="s">
-        <v>510</v>
-      </c>
       <c r="D84" s="18" t="s">
+        <v>516</v>
+      </c>
+      <c r="E84" s="18" t="s">
         <v>517</v>
       </c>
-      <c r="E84" s="18" t="s">
-        <v>518</v>
-      </c>
       <c r="F84" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G84" s="7" t="n">
         <v>0.01</v>
@@ -23007,19 +23004,19 @@
         <v>84</v>
       </c>
       <c r="B85" s="18" t="s">
+        <v>508</v>
+      </c>
+      <c r="C85" s="18" t="s">
         <v>509</v>
       </c>
-      <c r="C85" s="18" t="s">
-        <v>510</v>
-      </c>
       <c r="D85" s="16" t="s">
+        <v>518</v>
+      </c>
+      <c r="E85" s="18" t="s">
         <v>519</v>
       </c>
-      <c r="E85" s="18" t="s">
-        <v>520</v>
-      </c>
       <c r="F85" s="18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G85" s="7"/>
       <c r="H85" s="7"/>
@@ -23051,19 +23048,19 @@
         <v>85</v>
       </c>
       <c r="B86" s="18" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C86" s="18" t="s">
+        <v>520</v>
+      </c>
+      <c r="D86" s="18" t="s">
         <v>521</v>
       </c>
-      <c r="D86" s="18" t="s">
+      <c r="E86" s="18" t="s">
         <v>522</v>
       </c>
-      <c r="E86" s="18" t="s">
-        <v>523</v>
-      </c>
       <c r="F86" s="18" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G86" s="7" t="n">
         <v>0.15</v>
@@ -23111,19 +23108,19 @@
         <v>86</v>
       </c>
       <c r="B87" s="18" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C87" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D87" s="18" t="s">
+        <v>523</v>
+      </c>
+      <c r="E87" s="16" t="s">
         <v>524</v>
       </c>
-      <c r="E87" s="16" t="s">
-        <v>525</v>
-      </c>
       <c r="F87" s="18" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G87" s="7"/>
       <c r="H87" s="7"/>
@@ -23169,16 +23166,16 @@
         <v>87</v>
       </c>
       <c r="B88" s="18" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C88" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D88" s="18" t="s">
+        <v>525</v>
+      </c>
+      <c r="E88" s="18" t="s">
         <v>526</v>
-      </c>
-      <c r="E88" s="18" t="s">
-        <v>527</v>
       </c>
       <c r="F88" s="16"/>
       <c r="G88" s="7" t="n">
@@ -23233,19 +23230,19 @@
         <v>88</v>
       </c>
       <c r="B89" s="18" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C89" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D89" s="18" t="s">
+        <v>527</v>
+      </c>
+      <c r="E89" s="18" t="s">
         <v>528</v>
       </c>
-      <c r="E89" s="18" t="s">
-        <v>529</v>
-      </c>
       <c r="F89" s="18" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G89" s="7" t="n">
         <v>0.05</v>
@@ -23279,19 +23276,19 @@
         <v>89</v>
       </c>
       <c r="B90" s="18" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C90" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D90" s="18" t="s">
+        <v>529</v>
+      </c>
+      <c r="E90" s="18" t="s">
         <v>530</v>
       </c>
-      <c r="E90" s="18" t="s">
-        <v>531</v>
-      </c>
       <c r="F90" s="18" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G90" s="7" t="n">
         <v>0.05</v>
@@ -23325,19 +23322,19 @@
         <v>90</v>
       </c>
       <c r="B91" s="18" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C91" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D91" s="16" t="s">
+        <v>531</v>
+      </c>
+      <c r="E91" s="18" t="s">
         <v>532</v>
       </c>
-      <c r="E91" s="18" t="s">
-        <v>533</v>
-      </c>
       <c r="F91" s="18" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G91" s="7" t="n">
         <v>0.05</v>
@@ -23371,19 +23368,19 @@
         <v>91</v>
       </c>
       <c r="B92" s="18" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C92" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D92" s="18" t="s">
+        <v>533</v>
+      </c>
+      <c r="E92" s="18" t="s">
         <v>534</v>
       </c>
-      <c r="E92" s="18" t="s">
-        <v>535</v>
-      </c>
       <c r="F92" s="18" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G92" s="7"/>
       <c r="H92" s="7"/>
@@ -23415,19 +23412,19 @@
         <v>92</v>
       </c>
       <c r="B93" s="18" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C93" s="18" t="s">
+        <v>535</v>
+      </c>
+      <c r="D93" s="18" t="s">
         <v>536</v>
       </c>
-      <c r="D93" s="18" t="s">
+      <c r="E93" s="18" t="s">
         <v>537</v>
       </c>
-      <c r="E93" s="18" t="s">
-        <v>538</v>
-      </c>
       <c r="F93" s="18" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G93" s="7" t="n">
         <v>0.02</v>
@@ -23461,19 +23458,19 @@
         <v>93</v>
       </c>
       <c r="B94" s="18" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C94" s="18" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D94" s="18" t="s">
+        <v>538</v>
+      </c>
+      <c r="E94" s="18" t="s">
         <v>539</v>
       </c>
-      <c r="E94" s="18" t="s">
-        <v>540</v>
-      </c>
       <c r="F94" s="18" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G94" s="7"/>
       <c r="H94" s="7" t="n">
@@ -23505,19 +23502,19 @@
         <v>94</v>
       </c>
       <c r="B95" s="18" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C95" s="18" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D95" s="18" t="s">
+        <v>540</v>
+      </c>
+      <c r="E95" s="18" t="s">
         <v>541</v>
       </c>
-      <c r="E95" s="18" t="s">
-        <v>542</v>
-      </c>
       <c r="F95" s="18" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G95" s="7"/>
       <c r="H95" s="7" t="n">
@@ -23549,19 +23546,19 @@
         <v>95</v>
       </c>
       <c r="B96" s="18" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C96" s="18" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D96" s="18" t="s">
+        <v>542</v>
+      </c>
+      <c r="E96" s="18" t="s">
         <v>543</v>
       </c>
-      <c r="E96" s="18" t="s">
-        <v>544</v>
-      </c>
       <c r="F96" s="18" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G96" s="7"/>
       <c r="H96" s="7" t="n">
@@ -23593,19 +23590,19 @@
         <v>96</v>
       </c>
       <c r="B97" s="18" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C97" s="18" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D97" s="18" t="s">
+        <v>544</v>
+      </c>
+      <c r="E97" s="18" t="s">
         <v>545</v>
       </c>
-      <c r="E97" s="18" t="s">
-        <v>546</v>
-      </c>
       <c r="F97" s="18" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G97" s="7"/>
       <c r="H97" s="7" t="n">
@@ -23637,19 +23634,19 @@
         <v>97</v>
       </c>
       <c r="B98" s="18" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C98" s="18" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D98" s="18" t="s">
+        <v>546</v>
+      </c>
+      <c r="E98" s="18" t="s">
         <v>547</v>
       </c>
-      <c r="E98" s="18" t="s">
-        <v>548</v>
-      </c>
       <c r="F98" s="18" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G98" s="7"/>
       <c r="H98" s="7"/>
@@ -23693,19 +23690,19 @@
         <v>98</v>
       </c>
       <c r="B99" s="18" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C99" s="18" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D99" s="16" t="s">
+        <v>548</v>
+      </c>
+      <c r="E99" s="18" t="s">
         <v>549</v>
       </c>
-      <c r="E99" s="18" t="s">
-        <v>550</v>
-      </c>
       <c r="F99" s="18" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G99" s="7"/>
       <c r="H99" s="7" t="n">
@@ -23751,19 +23748,19 @@
         <v>99</v>
       </c>
       <c r="B100" s="18" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C100" s="18" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D100" s="18" t="s">
+        <v>550</v>
+      </c>
+      <c r="E100" s="18" t="s">
         <v>551</v>
       </c>
-      <c r="E100" s="18" t="s">
-        <v>552</v>
-      </c>
       <c r="F100" s="18" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G100" s="7"/>
       <c r="H100" s="7"/>
@@ -23797,19 +23794,19 @@
         <v>100</v>
       </c>
       <c r="B101" s="18" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C101" s="18" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D101" s="18" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E101" s="18" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F101" s="18" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G101" s="7" t="n">
         <v>0.01</v>
@@ -23855,19 +23852,19 @@
         <v>101</v>
       </c>
       <c r="B102" s="18" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C102" s="18" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D102" s="18" t="s">
+        <v>553</v>
+      </c>
+      <c r="E102" s="18" t="s">
         <v>554</v>
       </c>
-      <c r="E102" s="18" t="s">
-        <v>555</v>
-      </c>
       <c r="F102" s="18" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G102" s="7" t="n">
         <v>0.01</v>
@@ -23901,19 +23898,19 @@
         <v>102</v>
       </c>
       <c r="B103" s="18" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C103" s="18" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D103" s="16" t="s">
+        <v>555</v>
+      </c>
+      <c r="E103" s="16" t="s">
         <v>556</v>
       </c>
-      <c r="E103" s="16" t="s">
-        <v>557</v>
-      </c>
       <c r="F103" s="18" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G103" s="7" t="n">
         <v>0.01</v>
@@ -23944,7 +23941,7 @@
     </row>
     <row r="104" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D104" s="4" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G104" s="19" t="n">
         <f aca="false">SUM(G2:G103)</f>
@@ -24021,7 +24018,7 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="12" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
   </sheetData>

--- a/docs/tai-ve/Phan-tich-khoi-luong-MD-APIC.xlsx
+++ b/docs/tai-ve/Phan-tich-khoi-luong-MD-APIC.xlsx
@@ -324,10 +324,10 @@
     <t xml:space="preserve">Hien</t>
   </si>
   <si>
-    <t xml:space="preserve">Teton Bros, ALLTERRAIN, Mont-Bell, DESCENTE GOLF, Snowpeak (4 lô trên Plantable)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Không giao thêm. Tháng 11–12 khá cao (mẫu SKI, 14 mã vào chuyền tháng 12)</t>
+    <t xml:space="preserve">Teton Bros, ALLTERRAIN, Mont-Bell, DESCENTE GOLF, Snowpeak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Không giao thêm. Tháng 11–12 khá cao (mẫu SKI, 12 mã vào chuyền tháng 12)</t>
   </si>
   <si>
     <t xml:space="preserve">Nhu</t>
@@ -5483,25 +5483,25 @@
         <v>70</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="E5" s="10" t="n">
         <v>0.15</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5512,22 +5512,22 @@
         <v>71</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>0.35</v>
@@ -5541,25 +5541,25 @@
         <v>72</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="F7" s="10" t="n">
         <v>0.15</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.97</v>
+        <v>0.89</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5570,25 +5570,25 @@
         <v>73</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="F8" s="10" t="n">
         <v>0.11</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>0.68</v>
+        <v>0.54</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>0.79</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5599,25 +5599,25 @@
         <v>70</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5628,22 +5628,22 @@
         <v>71</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>0.35</v>
@@ -5657,25 +5657,25 @@
         <v>72</v>
       </c>
       <c r="C11" s="10" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>0.8</v>
+        <v>0.81</v>
       </c>
       <c r="F11" s="10" t="n">
         <v>0.15</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.97</v>
+        <v>0.89</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5686,25 +5686,25 @@
         <v>73</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="F12" s="10" t="n">
         <v>0.11</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>0.68</v>
+        <v>0.54</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>0.79</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5715,25 +5715,25 @@
         <v>70</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="F13" s="13" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5744,22 +5744,22 @@
         <v>71</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>0.35</v>
@@ -5773,25 +5773,25 @@
         <v>72</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>0.8</v>
+        <v>0.81</v>
       </c>
       <c r="F15" s="10" t="n">
         <v>0.15</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.97</v>
+        <v>0.89</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5802,25 +5802,25 @@
         <v>73</v>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="F16" s="10" t="n">
         <v>0.11</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>0.68</v>
+        <v>0.54</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>0.79</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5831,25 +5831,25 @@
         <v>70</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="F17" s="13" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5860,22 +5860,22 @@
         <v>71</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>0.93</v>
+        <v>0.94</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>0.35</v>
@@ -5889,25 +5889,25 @@
         <v>72</v>
       </c>
       <c r="C19" s="10" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>0.8</v>
+        <v>0.81</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>0.97</v>
+        <v>0.89</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5918,25 +5918,25 @@
         <v>73</v>
       </c>
       <c r="C20" s="10" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="F20" s="10" t="n">
         <v>0.11</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>0.68</v>
+        <v>0.54</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>0.79</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5947,25 +5947,25 @@
         <v>70</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="F21" s="13" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="H21" s="13" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5975,26 +5975,26 @@
       <c r="B22" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C22" s="10" t="n">
-        <v>1.38</v>
+      <c r="C22" s="13" t="n">
+        <v>1.41</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>0.93</v>
+        <v>0.94</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>0.56</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6005,25 +6005,25 @@
         <v>72</v>
       </c>
       <c r="C23" s="10" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>0.8</v>
+        <v>0.81</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>0.97</v>
+        <v>0.89</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6034,25 +6034,25 @@
         <v>73</v>
       </c>
       <c r="C24" s="10" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="F24" s="10" t="n">
         <v>0.11</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>0.68</v>
+        <v>0.54</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>0.79</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6112,7 +6112,7 @@
         <v>8</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I28" s="8" t="n">
         <v>3</v>
@@ -6141,7 +6141,7 @@
         <v>1</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I29" s="8" t="n">
         <v>2</v>
@@ -6170,7 +6170,7 @@
         <v>25</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I30" s="8" t="n">
         <v>11</v>
@@ -6199,7 +6199,7 @@
         <v>2</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I31" s="8" t="n">
         <v>7</v>
@@ -6228,7 +6228,7 @@
         <v>10</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I32" s="8" t="n">
         <v>8</v>
@@ -6257,7 +6257,7 @@
         <v>5</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I33" s="8" t="n">
         <v>3</v>
@@ -6286,7 +6286,7 @@
         <v>26</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I34" s="8" t="n">
         <v>14</v>
@@ -6315,7 +6315,7 @@
         <v>6</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I35" s="8" t="n">
         <v>14</v>
@@ -6460,7 +6460,7 @@
         <v>93</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I40" s="8" t="n">
         <v>92</v>
@@ -6489,7 +6489,7 @@
         <v>18</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="I41" s="8" t="n">
         <v>20</v>
@@ -6518,7 +6518,7 @@
         <v>87</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="I42" s="8" t="n">
         <v>79</v>
@@ -6547,7 +6547,7 @@
         <v>23</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="I43" s="8" t="n">
         <v>35</v>
